--- a/outputs/results_report.xlsx
+++ b/outputs/results_report.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -778,32 +778,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.04 +/- 0.00</t>
+          <t>0.02 +/- 0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.59 +/- 0.12</t>
+          <t>0.33 +/- 0.02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.50 +/- 0.02</t>
+          <t>3.69 +/- 0.04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.22 +/- 0.30</t>
+          <t>11.84 +/- 0.44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.15 +/- 0.01</t>
+          <t>0.05 +/- 0.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24.86 +/- 0.64</t>
+          <t>63.56 +/- 1.17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>241.20 +/- 1.58</t>
+          <t>159.50 +/- 1.32</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.04 +/- 0.00</t>
+          <t>0.02 +/- 0.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.89 +/- 0.31</t>
+          <t>0.33 +/- 0.02</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2.30 +/- 0.01</t>
+          <t>2.52 +/- 0.01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.34 +/- 0.10</t>
+          <t>5.21 +/- 0.02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.16 +/- 0.01</t>
+          <t>0.05 +/- 0.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18.42 +/- 0.36</t>
+          <t>24.77 +/- 0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>241.80 +/- 1.49</t>
+          <t>159.98 +/- 1.46</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18.40 +/- 0.09</t>
+          <t>13.30 +/- 0.11</t>
         </is>
       </c>
     </row>
@@ -902,32 +902,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.02 +/- 0.00</t>
+          <t>0.01 +/- 0.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.38 +/- 0.03</t>
+          <t>0.22 +/- 0.02</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3.30 +/- 0.03</t>
+          <t>7.38 +/- 0.14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.67 +/- 0.41</t>
+          <t>22.26 +/- 0.72</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.07 +/- 0.00</t>
+          <t>0.01 +/- 0.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50.63 +/- 0.89</t>
+          <t>178.84 +/- 3.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>179.23 +/- 1.64</t>
+          <t>78.58 +/- 1.26</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -964,32 +964,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02 +/- 0.00</t>
+          <t>0.01 +/- 0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.39 +/- 0.03</t>
+          <t>0.23 +/- 0.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.49 +/- 0.01</t>
+          <t>2.53 +/- 0.02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.22 +/- 0.02</t>
+          <t>5.11 +/- 0.02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.07 +/- 0.00</t>
+          <t>0.01 +/- 0.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24.65 +/- 0.30</t>
+          <t>25.10 +/- 0.32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>179.87 +/- 1.54</t>
+          <t>80.17 +/- 1.04</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14.85 +/- 0.12</t>
+          <t>6.68 +/- 0.08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -1036,7 +1036,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -1184,52 +1184,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.03852554652116558</v>
+        <v>0.02045199094649507</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001360027803736226</v>
+        <v>0.000782948116804992</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5856132006961919</v>
+        <v>0.3263240095474212</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1181485370659881</v>
+        <v>0.02029511473627826</v>
       </c>
       <c r="J2" t="n">
-        <v>2.501207454224977</v>
+        <v>3.688513541790326</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01754774600638448</v>
+        <v>0.03809455999805379</v>
       </c>
       <c r="L2" t="n">
-        <v>8.221058644261518</v>
+        <v>11.83980665489334</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3047112560254077</v>
+        <v>0.4424963610728582</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1549709562369991</v>
+        <v>0.0544327569483957</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0059922732440122</v>
+        <v>0.002280487051051127</v>
       </c>
       <c r="P2" t="n">
-        <v>24.86323269592794</v>
+        <v>63.5596912520793</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6427744334433476</v>
+        <v>1.167887824413645</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9997602814352274</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003363676322499163</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>241.2041666666667</v>
+        <v>159.5041666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>1.578978602528225</v>
+        <v>1.319135950191734</v>
       </c>
       <c r="V2" t="n">
         <v>20</v>
@@ -1261,58 +1261,58 @@
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04008067335630813</v>
+        <v>0.02029849319924581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002702342240834363</v>
+        <v>0.0006823553138031169</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8903665098543049</v>
+        <v>0.3313791086666072</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3093086455389402</v>
+        <v>0.02254319616277451</v>
       </c>
       <c r="J3" t="n">
-        <v>2.296685718650681</v>
+        <v>2.523635753590885</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01060696844345413</v>
+        <v>0.0146145184182918</v>
       </c>
       <c r="L3" t="n">
-        <v>5.339314253846497</v>
+        <v>5.209045994820083</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09922236453368816</v>
+        <v>0.02195124801776444</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1617234606599837</v>
+        <v>0.05416745005348352</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01145694980681117</v>
+        <v>0.002038016734134721</v>
       </c>
       <c r="P3" t="n">
-        <v>18.4187657772772</v>
+        <v>24.76855083326571</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3583071241109085</v>
+        <v>0.2932485325551993</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9983094012616824</v>
+        <v>0.9999592583806827</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001282965242754486</v>
+        <v>8.332596749629817e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>241.7958333333333</v>
+        <v>159.9833333333333</v>
       </c>
       <c r="U3" t="n">
-        <v>1.487196990544874</v>
+        <v>1.463583403752564</v>
       </c>
       <c r="V3" t="n">
-        <v>18.39602308211196</v>
+        <v>13.30253602218605</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08875064137030494</v>
+        <v>0.1129788348611653</v>
       </c>
     </row>
     <row r="4">
@@ -1335,40 +1335,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.02443435453611862</v>
+        <v>0.008400035698051667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009848167605312048</v>
+        <v>0.0006253465505873134</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3778275857971077</v>
+        <v>0.2235874857986331</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03118823437269624</v>
+        <v>0.02096532388251577</v>
       </c>
       <c r="J4" t="n">
-        <v>3.295077109758899</v>
+        <v>7.375197407186162</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03402661333846715</v>
+        <v>0.1378048931498083</v>
       </c>
       <c r="L4" t="n">
-        <v>10.66506614686472</v>
+        <v>22.26468345784561</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4102600901274898</v>
+        <v>0.7162572442610092</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07306484382127067</v>
+        <v>0.01102204800692406</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003279168447026605</v>
+        <v>0.0008621468018963727</v>
       </c>
       <c r="P4" t="n">
-        <v>50.63495590810204</v>
+        <v>178.8427342251462</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.892656611485048</v>
+        <v>3.065483464075587</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>179.2291666666667</v>
+        <v>78.57916666666667</v>
       </c>
       <c r="U4" t="n">
-        <v>1.640424573114747</v>
+        <v>1.258395404694679</v>
       </c>
       <c r="V4" t="n">
         <v>20</v>
@@ -1412,40 +1412,40 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02458333740028499</v>
+        <v>0.008676310008373666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0008005719949096322</v>
+        <v>0.0005206261361274917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3880205449008258</v>
+        <v>0.2259955110511915</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02525381018031835</v>
+        <v>0.01610905016821948</v>
       </c>
       <c r="J5" t="n">
-        <v>2.494918170660126</v>
+        <v>2.533994141978013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01434538353265071</v>
+        <v>0.02018371660017607</v>
       </c>
       <c r="L5" t="n">
-        <v>5.215213828672037</v>
+        <v>5.109212453531901</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02354686398174903</v>
+        <v>0.02498543324599337</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07368603016055245</v>
+        <v>0.0116129750057529</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002643378925139322</v>
+        <v>0.0007660890930389553</v>
       </c>
       <c r="P5" t="n">
-        <v>24.64888264067234</v>
+        <v>25.10303092133324</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2966020463327395</v>
+        <v>0.3216362757092623</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1454,16 +1454,16 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>179.8708333333333</v>
+        <v>80.17083333333333</v>
       </c>
       <c r="U5" t="n">
-        <v>1.535659073132838</v>
+        <v>1.044887668754412</v>
       </c>
       <c r="V5" t="n">
-        <v>14.85025963134395</v>
+        <v>6.683333333333334</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1202105641362985</v>
+        <v>0.08219894133025926</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1482,7 @@
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1494,14 +1494,14 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="20" customWidth="1" min="25" max="25"/>
@@ -1670,82 +1670,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0015551268351425</v>
+        <v>-0.0001534977472492</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0026436539388228</v>
+        <v>0.0006336021042326</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.304753309158113</v>
+        <v>0.0050550991191859</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3505232709456123</v>
+        <v>0.0210435724031448</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2045217355742958</v>
+        <v>-1.164877788199442</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0167454391194054</v>
+        <v>0.0375053088299448</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.881744390415022</v>
+        <v>-6.630760660073262</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3153755880068606</v>
+        <v>0.4411023928630265</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0067525044229846</v>
+        <v>-0.0002653068949121</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0111546902454499</v>
+        <v>0.0019354942353225</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-6.444466918650742</v>
+        <v>-38.7911404188136</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6601524108017962</v>
+        <v>1.200329185441725</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0014508801735448</v>
+        <v>-4.074161931733415e-05</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0013669266006428</v>
+        <v>8.332596749629817e-05</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5916666666666667</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.77646959422905</v>
+        <v>1.3969472151053</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1.603976917888044</v>
+        <v>-6.697463977813952</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0887506413703049</v>
+        <v>0.1129788348611652</v>
       </c>
       <c r="AC2" t="b">
         <v>1</v>
@@ -1763,55 +1763,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0001489828641663</v>
+        <v>0.0002762743103219</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008442375605347</v>
+        <v>0.0005570317068262</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0101929591037181</v>
+        <v>0.0024080252525583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0425706944114409</v>
+        <v>0.0166343877829503</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8001589390987737</v>
+        <v>-4.841203265208149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0335674071229063</v>
+        <v>0.1377741167654058</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.449852318192687</v>
+        <v>-17.15547100431371</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4123040336767956</v>
+        <v>0.7152127504907289</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0006211863392817</v>
+        <v>0.0005909269988288</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0028812219951488</v>
+        <v>0.0007913656078139001</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-25.9860732674297</v>
+        <v>-153.739703303813</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8299659921633797</v>
+        <v>3.118455035374834</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -1826,19 +1826,19 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6416666666666667</v>
+        <v>1.591666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.732269035167044</v>
+        <v>1.084226539380186</v>
       </c>
       <c r="Z3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>-5.149740368656055</v>
+        <v>-13.31666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1202105641362985</v>
+        <v>0.08219894133025921</v>
       </c>
       <c r="AC3" t="b">
         <v>1</v>
@@ -3050,43 +3050,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145.377</v>
+        <v>48.124</v>
       </c>
       <c r="D2" t="n">
-        <v>245.772</v>
+        <v>86.374</v>
       </c>
       <c r="E2" t="n">
-        <v>145.897</v>
+        <v>49.071</v>
       </c>
       <c r="F2" t="n">
-        <v>247.687</v>
+        <v>88.363</v>
       </c>
       <c r="G2" t="n">
-        <v>583.252</v>
+        <v>129.139</v>
       </c>
       <c r="H2" t="n">
-        <v>2.247</v>
+        <v>2.249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.23</v>
+        <v>0.232</v>
       </c>
       <c r="J2" t="n">
-        <v>138.258</v>
+        <v>138.396</v>
       </c>
       <c r="K2" t="n">
         <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="M2" t="n">
-        <v>2396.633</v>
+        <v>1595.633</v>
       </c>
       <c r="N2" t="n">
-        <v>1401.633</v>
+        <v>1379.667</v>
       </c>
       <c r="O2" t="n">
-        <v>995</v>
+        <v>215.967</v>
       </c>
     </row>
     <row r="3">
@@ -3099,43 +3099,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>146.342</v>
+        <v>52.935</v>
       </c>
       <c r="D3" t="n">
-        <v>248.291</v>
+        <v>91.364</v>
       </c>
       <c r="E3" t="n">
-        <v>147.125</v>
+        <v>53.819</v>
       </c>
       <c r="F3" t="n">
-        <v>249.371</v>
+        <v>93.21899999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>590.829</v>
+        <v>142.778</v>
       </c>
       <c r="H3" t="n">
-        <v>2.208</v>
+        <v>2.232</v>
       </c>
       <c r="I3" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="J3" t="n">
-        <v>139.192</v>
+        <v>138.312</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.995</v>
       </c>
       <c r="L3" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2399.933</v>
+        <v>1596.3</v>
       </c>
       <c r="N3" t="n">
-        <v>1396.067</v>
+        <v>1360.567</v>
       </c>
       <c r="O3" t="n">
-        <v>1003.867</v>
+        <v>235.733</v>
       </c>
     </row>
     <row r="4">
@@ -3148,43 +3148,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79.833</v>
+        <v>1.074</v>
       </c>
       <c r="D4" t="n">
-        <v>141.421</v>
+        <v>12.802</v>
       </c>
       <c r="E4" t="n">
-        <v>80.658</v>
+        <v>4.206</v>
       </c>
       <c r="F4" t="n">
-        <v>143.054</v>
+        <v>15.047</v>
       </c>
       <c r="G4" t="n">
-        <v>321.853</v>
+        <v>2.91</v>
       </c>
       <c r="H4" t="n">
-        <v>2.349</v>
+        <v>10.265</v>
       </c>
       <c r="I4" t="n">
-        <v>0.304</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>182.508</v>
+        <v>159.692</v>
       </c>
       <c r="K4" t="n">
         <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>72.90000000000001</v>
+        <v>63.933</v>
       </c>
       <c r="M4" t="n">
-        <v>2393.6</v>
+        <v>1594.6</v>
       </c>
       <c r="N4" t="n">
-        <v>1835.8</v>
+        <v>1590.533</v>
       </c>
       <c r="O4" t="n">
-        <v>557.8</v>
+        <v>4.067</v>
       </c>
     </row>
     <row r="5">
@@ -3197,43 +3197,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.274</v>
+        <v>4.22</v>
       </c>
       <c r="D5" t="n">
-        <v>145.202</v>
+        <v>19.085</v>
       </c>
       <c r="E5" t="n">
-        <v>83.998</v>
+        <v>5.979</v>
       </c>
       <c r="F5" t="n">
-        <v>146.602</v>
+        <v>21.254</v>
       </c>
       <c r="G5" t="n">
-        <v>337.694</v>
+        <v>11.193</v>
       </c>
       <c r="H5" t="n">
-        <v>2.369</v>
+        <v>4.001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.306</v>
+        <v>0.49</v>
       </c>
       <c r="J5" t="n">
-        <v>183.5</v>
+        <v>162.179</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>18.094</v>
       </c>
       <c r="L5" t="n">
-        <v>73.467</v>
+        <v>71.667</v>
       </c>
       <c r="M5" t="n">
-        <v>2401.667</v>
+        <v>1601.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1828.5</v>
+        <v>1592.5</v>
       </c>
       <c r="O5" t="n">
-        <v>573.167</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6">
@@ -3246,43 +3246,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.265</v>
+        <v>0.023</v>
       </c>
       <c r="D6" t="n">
-        <v>37.397</v>
+        <v>0.626</v>
       </c>
       <c r="E6" t="n">
-        <v>19.302</v>
+        <v>3.689</v>
       </c>
       <c r="F6" t="n">
-        <v>39.235</v>
+        <v>11.84</v>
       </c>
       <c r="G6" t="n">
-        <v>73.48999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="H6" t="n">
-        <v>2.578</v>
+        <v>25.597</v>
       </c>
       <c r="I6" t="n">
-        <v>0.396</v>
+        <v>0.999</v>
       </c>
       <c r="J6" t="n">
-        <v>228.933</v>
+        <v>159.492</v>
       </c>
       <c r="K6" t="n">
         <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>91.56699999999999</v>
+        <v>63.867</v>
       </c>
       <c r="M6" t="n">
-        <v>2399.133</v>
+        <v>1588.467</v>
       </c>
       <c r="N6" t="n">
-        <v>2275.3</v>
+        <v>1588.3</v>
       </c>
       <c r="O6" t="n">
-        <v>123.833</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="7">
@@ -3295,43 +3295,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.02</v>
+        <v>0.955</v>
       </c>
       <c r="D7" t="n">
-        <v>40.154</v>
+        <v>10.88</v>
       </c>
       <c r="E7" t="n">
-        <v>21.046</v>
+        <v>3.288</v>
       </c>
       <c r="F7" t="n">
-        <v>41.797</v>
+        <v>12.902</v>
       </c>
       <c r="G7" t="n">
-        <v>81.15600000000001</v>
+        <v>2.551</v>
       </c>
       <c r="H7" t="n">
-        <v>2.493</v>
+        <v>7.089</v>
       </c>
       <c r="I7" t="n">
-        <v>0.391</v>
+        <v>0.789</v>
       </c>
       <c r="J7" t="n">
-        <v>229.083</v>
+        <v>159.512</v>
       </c>
       <c r="K7" t="n">
-        <v>19.981</v>
+        <v>15.147</v>
       </c>
       <c r="L7" t="n">
-        <v>91.767</v>
+        <v>84.233</v>
       </c>
       <c r="M7" t="n">
-        <v>2402</v>
+        <v>1593.567</v>
       </c>
       <c r="N7" t="n">
-        <v>2267.433</v>
+        <v>1590.2</v>
       </c>
       <c r="O7" t="n">
-        <v>134.567</v>
+        <v>3.367</v>
       </c>
     </row>
     <row r="8">
@@ -3344,43 +3344,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.392</v>
+        <v>0.02</v>
       </c>
       <c r="D8" t="n">
-        <v>7.548</v>
+        <v>0.326</v>
       </c>
       <c r="E8" t="n">
-        <v>2.683</v>
+        <v>3.689</v>
       </c>
       <c r="F8" t="n">
-        <v>9.983000000000001</v>
+        <v>11.84</v>
       </c>
       <c r="G8" t="n">
-        <v>1.592</v>
+        <v>0.054</v>
       </c>
       <c r="H8" t="n">
-        <v>9.965999999999999</v>
+        <v>40.708</v>
       </c>
       <c r="I8" t="n">
-        <v>0.914</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>240.454</v>
+        <v>159.504</v>
       </c>
       <c r="K8" t="n">
         <v>20</v>
       </c>
       <c r="L8" t="n">
-        <v>96.133</v>
+        <v>63.833</v>
       </c>
       <c r="M8" t="n">
-        <v>2396.067</v>
+        <v>1588.567</v>
       </c>
       <c r="N8" t="n">
-        <v>2393.067</v>
+        <v>1588.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="9">
@@ -3393,43 +3393,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.089</v>
+        <v>0.103</v>
       </c>
       <c r="D9" t="n">
-        <v>10.549</v>
+        <v>4.953</v>
       </c>
       <c r="E9" t="n">
-        <v>3.043</v>
+        <v>2.607</v>
       </c>
       <c r="F9" t="n">
-        <v>12.456</v>
+        <v>8.398</v>
       </c>
       <c r="G9" t="n">
-        <v>4.411</v>
+        <v>0.269</v>
       </c>
       <c r="H9" t="n">
-        <v>6.646</v>
+        <v>11.387</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="J9" t="n">
-        <v>241.204</v>
+        <v>159.962</v>
       </c>
       <c r="K9" t="n">
-        <v>18.994</v>
+        <v>13.602</v>
       </c>
       <c r="L9" t="n">
-        <v>101.633</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>2401.967</v>
+        <v>1593.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2395.533</v>
+        <v>1593.767</v>
       </c>
       <c r="O9" t="n">
-        <v>6.433</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="10">
@@ -3442,43 +3442,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="D10" t="n">
-        <v>0.586</v>
+        <v>0.326</v>
       </c>
       <c r="E10" t="n">
-        <v>2.501</v>
+        <v>3.689</v>
       </c>
       <c r="F10" t="n">
-        <v>8.221</v>
+        <v>11.84</v>
       </c>
       <c r="G10" t="n">
-        <v>0.155</v>
+        <v>0.054</v>
       </c>
       <c r="H10" t="n">
-        <v>24.863</v>
+        <v>63.56</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>241.204</v>
+        <v>159.504</v>
       </c>
       <c r="K10" t="n">
         <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>96.56699999999999</v>
+        <v>63.833</v>
       </c>
       <c r="M10" t="n">
-        <v>2399.633</v>
+        <v>1588.567</v>
       </c>
       <c r="N10" t="n">
-        <v>2399.433</v>
+        <v>1588.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="11">
@@ -3491,43 +3491,43 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D11" t="n">
-        <v>0.89</v>
+        <v>0.331</v>
       </c>
       <c r="E11" t="n">
-        <v>2.297</v>
+        <v>2.524</v>
       </c>
       <c r="F11" t="n">
-        <v>5.339</v>
+        <v>5.209</v>
       </c>
       <c r="G11" t="n">
-        <v>0.162</v>
+        <v>0.054</v>
       </c>
       <c r="H11" t="n">
-        <v>18.419</v>
+        <v>24.769</v>
       </c>
       <c r="I11" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>241.796</v>
+        <v>159.983</v>
       </c>
       <c r="K11" t="n">
-        <v>18.396</v>
+        <v>13.303</v>
       </c>
       <c r="L11" t="n">
-        <v>105.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>2406.733</v>
+        <v>1596.367</v>
       </c>
       <c r="N11" t="n">
-        <v>2406.633</v>
+        <v>1596.333</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="12">
@@ -3540,40 +3540,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="D12" t="n">
-        <v>0.508</v>
+        <v>0.326</v>
       </c>
       <c r="E12" t="n">
-        <v>2.501</v>
+        <v>3.689</v>
       </c>
       <c r="F12" t="n">
-        <v>8.221</v>
+        <v>11.84</v>
       </c>
       <c r="G12" t="n">
-        <v>0.153</v>
+        <v>0.054</v>
       </c>
       <c r="H12" t="n">
-        <v>39.826</v>
+        <v>88.142</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>241.229</v>
+        <v>159.504</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>96.56699999999999</v>
+        <v>63.833</v>
       </c>
       <c r="M12" t="n">
-        <v>2399.8</v>
+        <v>1588.567</v>
       </c>
       <c r="N12" t="n">
-        <v>2399.633</v>
+        <v>1588.4</v>
       </c>
       <c r="O12" t="n">
         <v>0.167</v>
@@ -3589,43 +3589,43 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.037</v>
+        <v>0.02</v>
       </c>
       <c r="D13" t="n">
-        <v>0.481</v>
+        <v>0.331</v>
       </c>
       <c r="E13" t="n">
-        <v>2.292</v>
+        <v>2.524</v>
       </c>
       <c r="F13" t="n">
-        <v>5.276</v>
+        <v>5.209</v>
       </c>
       <c r="G13" t="n">
-        <v>0.151</v>
+        <v>0.054</v>
       </c>
       <c r="H13" t="n">
-        <v>32.032</v>
+        <v>39.754</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>242.05</v>
+        <v>159.912</v>
       </c>
       <c r="K13" t="n">
-        <v>18.396</v>
+        <v>13.297</v>
       </c>
       <c r="L13" t="n">
-        <v>105.333</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>2408.7</v>
+        <v>1595.767</v>
       </c>
       <c r="N13" t="n">
-        <v>2408.6</v>
+        <v>1595.767</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3638,40 +3638,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="D14" t="n">
-        <v>0.508</v>
+        <v>0.326</v>
       </c>
       <c r="E14" t="n">
-        <v>2.501</v>
+        <v>3.689</v>
       </c>
       <c r="F14" t="n">
-        <v>8.221</v>
+        <v>11.84</v>
       </c>
       <c r="G14" t="n">
-        <v>0.153</v>
+        <v>0.054</v>
       </c>
       <c r="H14" t="n">
-        <v>49.806</v>
+        <v>104.129</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>241.229</v>
+        <v>159.504</v>
       </c>
       <c r="K14" t="n">
         <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>96.56699999999999</v>
+        <v>63.833</v>
       </c>
       <c r="M14" t="n">
-        <v>2399.8</v>
+        <v>1588.567</v>
       </c>
       <c r="N14" t="n">
-        <v>2399.633</v>
+        <v>1588.4</v>
       </c>
       <c r="O14" t="n">
         <v>0.167</v>
@@ -3687,43 +3687,43 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.037</v>
+        <v>0.02</v>
       </c>
       <c r="D15" t="n">
-        <v>0.481</v>
+        <v>0.331</v>
       </c>
       <c r="E15" t="n">
-        <v>2.292</v>
+        <v>2.524</v>
       </c>
       <c r="F15" t="n">
-        <v>5.276</v>
+        <v>5.209</v>
       </c>
       <c r="G15" t="n">
-        <v>0.151</v>
+        <v>0.054</v>
       </c>
       <c r="H15" t="n">
-        <v>41.147</v>
+        <v>49.741</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>242.05</v>
+        <v>159.912</v>
       </c>
       <c r="K15" t="n">
-        <v>18.396</v>
+        <v>13.297</v>
       </c>
       <c r="L15" t="n">
-        <v>105.333</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>2408.7</v>
+        <v>1595.767</v>
       </c>
       <c r="N15" t="n">
-        <v>2408.6</v>
+        <v>1595.767</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3890,40 +3890,40 @@
         <v>2025</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0373</v>
+        <v>0.0184</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5107</v>
+        <v>0.2608</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4788</v>
+        <v>3.7454</v>
       </c>
       <c r="K2" t="n">
-        <v>8.6472</v>
+        <v>13.4055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.151</v>
+        <v>0.0485</v>
       </c>
       <c r="M2" t="n">
-        <v>25.3713</v>
+        <v>66.50369999999999</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>242.875</v>
+        <v>158.5</v>
       </c>
       <c r="P2" t="n">
         <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="R2" t="n">
-        <v>2421</v>
+        <v>1590</v>
       </c>
       <c r="S2" t="n">
-        <v>2421</v>
+        <v>1590</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -3955,40 +3955,40 @@
         <v>2026</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0344</v>
+        <v>0.0191</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3609</v>
+        <v>0.2753</v>
       </c>
       <c r="J3" t="n">
-        <v>2.534</v>
+        <v>3.6252</v>
       </c>
       <c r="K3" t="n">
-        <v>7.5444</v>
+        <v>10.6103</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1394</v>
+        <v>0.0507</v>
       </c>
       <c r="M3" t="n">
-        <v>24.1449</v>
+        <v>63.8039</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>242.875</v>
+        <v>159.125</v>
       </c>
       <c r="P3" t="n">
         <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="R3" t="n">
-        <v>2395</v>
+        <v>1586</v>
       </c>
       <c r="S3" t="n">
-        <v>2395</v>
+        <v>1586</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -4020,43 +4020,43 @@
         <v>2027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0342</v>
+        <v>0.0182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4795</v>
+        <v>0.2535</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5414</v>
+        <v>3.7176</v>
       </c>
       <c r="K4" t="n">
-        <v>8.3864</v>
+        <v>12.5372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1324</v>
+        <v>0.0468</v>
       </c>
       <c r="M4" t="n">
-        <v>28.898</v>
+        <v>66.164</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>232.375</v>
+        <v>154.375</v>
       </c>
       <c r="P4" t="n">
         <v>20</v>
       </c>
       <c r="Q4" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="R4" t="n">
-        <v>2339</v>
+        <v>1555</v>
       </c>
       <c r="S4" t="n">
-        <v>2339</v>
+        <v>1554</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4085,40 +4085,40 @@
         <v>2028</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0406</v>
+        <v>0.0212</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6472</v>
+        <v>0.3119</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5302</v>
+        <v>3.7061</v>
       </c>
       <c r="K5" t="n">
-        <v>8.273400000000001</v>
+        <v>10.638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1645</v>
+        <v>0.0558</v>
       </c>
       <c r="M5" t="n">
-        <v>26.4072</v>
+        <v>62.9975</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>243.25</v>
+        <v>158.125</v>
       </c>
       <c r="P5" t="n">
         <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="R5" t="n">
-        <v>2419</v>
+        <v>1581</v>
       </c>
       <c r="S5" t="n">
-        <v>2419</v>
+        <v>1581</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -4150,40 +4150,40 @@
         <v>2029</v>
       </c>
       <c r="H6" t="n">
-        <v>0.037</v>
+        <v>0.0215</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4475</v>
+        <v>0.3148</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4959</v>
+        <v>3.5379</v>
       </c>
       <c r="K6" t="n">
-        <v>8.1953</v>
+        <v>11.382</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1481</v>
+        <v>0.0591</v>
       </c>
       <c r="M6" t="n">
-        <v>24.4962</v>
+        <v>58.5469</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>240.25</v>
+        <v>164.75</v>
       </c>
       <c r="P6" t="n">
         <v>20</v>
       </c>
       <c r="Q6" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="R6" t="n">
-        <v>2375</v>
+        <v>1635</v>
       </c>
       <c r="S6" t="n">
-        <v>2375</v>
+        <v>1635</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -4215,40 +4215,40 @@
         <v>2030</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0391</v>
+        <v>0.0211</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4232</v>
+        <v>0.4473</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5884</v>
+        <v>3.7808</v>
       </c>
       <c r="K7" t="n">
-        <v>11.2204</v>
+        <v>13.3568</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1543</v>
+        <v>0.0547</v>
       </c>
       <c r="M7" t="n">
-        <v>26.8893</v>
+        <v>69.9956</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>236.625</v>
+        <v>155.625</v>
       </c>
       <c r="P7" t="n">
         <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="R7" t="n">
-        <v>2336</v>
+        <v>1535</v>
       </c>
       <c r="S7" t="n">
-        <v>2336</v>
+        <v>1535</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -4280,40 +4280,40 @@
         <v>2031</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0393</v>
+        <v>0.0185</v>
       </c>
       <c r="I8" t="n">
-        <v>0.429</v>
+        <v>0.4276</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5318</v>
+        <v>3.7417</v>
       </c>
       <c r="K8" t="n">
-        <v>7.8226</v>
+        <v>10.9129</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1551</v>
+        <v>0.048</v>
       </c>
       <c r="M8" t="n">
-        <v>25.7695</v>
+        <v>64.12739999999999</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>236.75</v>
+        <v>156.125</v>
       </c>
       <c r="P8" t="n">
         <v>20</v>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="R8" t="n">
-        <v>2372</v>
+        <v>1563</v>
       </c>
       <c r="S8" t="n">
-        <v>2372</v>
+        <v>1563</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -4345,40 +4345,40 @@
         <v>2032</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0362</v>
+        <v>0.0208</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4165</v>
+        <v>0.2967</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5062</v>
+        <v>3.8335</v>
       </c>
       <c r="K9" t="n">
-        <v>7.463</v>
+        <v>11.285</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1442</v>
+        <v>0.0546</v>
       </c>
       <c r="M9" t="n">
-        <v>26.1923</v>
+        <v>62.6375</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>238.75</v>
+        <v>157.25</v>
       </c>
       <c r="P9" t="n">
         <v>20</v>
       </c>
       <c r="Q9" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="R9" t="n">
-        <v>2361</v>
+        <v>1567</v>
       </c>
       <c r="S9" t="n">
-        <v>2361</v>
+        <v>1567</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -4410,43 +4410,43 @@
         <v>2033</v>
       </c>
       <c r="H10" t="n">
-        <v>0.049</v>
+        <v>0.025</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4494</v>
+        <v>0.4084</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4588</v>
+        <v>3.6315</v>
       </c>
       <c r="K10" t="n">
-        <v>6.7621</v>
+        <v>10.2562</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1988</v>
+        <v>0.0668</v>
       </c>
       <c r="M10" t="n">
-        <v>23.3514</v>
+        <v>61.4891</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9972</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>243.625</v>
+        <v>160.375</v>
       </c>
       <c r="P10" t="n">
         <v>20</v>
       </c>
       <c r="Q10" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="R10" t="n">
-        <v>2448</v>
+        <v>1603</v>
       </c>
       <c r="S10" t="n">
-        <v>2447</v>
+        <v>1603</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4475,40 +4475,40 @@
         <v>2034</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0391</v>
+        <v>0.0189</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5514</v>
+        <v>0.2765</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4729</v>
+        <v>3.6709</v>
       </c>
       <c r="K11" t="n">
-        <v>9.031599999999999</v>
+        <v>13.3724</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1575</v>
+        <v>0.0493</v>
       </c>
       <c r="M11" t="n">
-        <v>26.141</v>
+        <v>67.42659999999999</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>241.75</v>
+        <v>156.75</v>
       </c>
       <c r="P11" t="n">
         <v>20</v>
       </c>
       <c r="Q11" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>2388</v>
+        <v>1556</v>
       </c>
       <c r="S11" t="n">
-        <v>2388</v>
+        <v>1556</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -4540,40 +4540,40 @@
         <v>2035</v>
       </c>
       <c r="H12" t="n">
-        <v>0.046</v>
+        <v>0.0195</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8936</v>
+        <v>0.3302</v>
       </c>
       <c r="J12" t="n">
-        <v>2.4621</v>
+        <v>3.7973</v>
       </c>
       <c r="K12" t="n">
-        <v>7.8827</v>
+        <v>12.2414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1899</v>
+        <v>0.0525</v>
       </c>
       <c r="M12" t="n">
-        <v>21.7814</v>
+        <v>58.8544</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9959</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>247.875</v>
+        <v>161.625</v>
       </c>
       <c r="P12" t="n">
         <v>20</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R12" t="n">
-        <v>2440</v>
+        <v>1606</v>
       </c>
       <c r="S12" t="n">
-        <v>2440</v>
+        <v>1606</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -4605,40 +4605,40 @@
         <v>2036</v>
       </c>
       <c r="H13" t="n">
-        <v>0.039</v>
+        <v>0.0216</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7629</v>
+        <v>0.4187</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5426</v>
+        <v>3.6846</v>
       </c>
       <c r="K13" t="n">
-        <v>8.730399999999999</v>
+        <v>12.6192</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1529</v>
+        <v>0.0585</v>
       </c>
       <c r="M13" t="n">
-        <v>26.4662</v>
+        <v>60.2233</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>235.5</v>
+        <v>162.5</v>
       </c>
       <c r="P13" t="n">
         <v>20</v>
       </c>
       <c r="Q13" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="R13" t="n">
-        <v>2368</v>
+        <v>1619</v>
       </c>
       <c r="S13" t="n">
-        <v>2368</v>
+        <v>1619</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -4670,40 +4670,40 @@
         <v>2037</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0329</v>
+        <v>0.0194</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5013</v>
+        <v>0.2812</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4725</v>
+        <v>3.7503</v>
       </c>
       <c r="K14" t="n">
-        <v>7.5323</v>
+        <v>10.9917</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1319</v>
+        <v>0.0511</v>
       </c>
       <c r="M14" t="n">
-        <v>24.3772</v>
+        <v>62.6049</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>240.625</v>
+        <v>157.75</v>
       </c>
       <c r="P14" t="n">
         <v>20</v>
       </c>
       <c r="Q14" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="R14" t="n">
-        <v>2403</v>
+        <v>1581</v>
       </c>
       <c r="S14" t="n">
-        <v>2403</v>
+        <v>1581</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -4735,40 +4735,40 @@
         <v>2038</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0378</v>
+        <v>0.0207</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6615</v>
+        <v>0.4105</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5022</v>
+        <v>3.6424</v>
       </c>
       <c r="K15" t="n">
-        <v>7.9997</v>
+        <v>10.4433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1511</v>
+        <v>0.0559</v>
       </c>
       <c r="M15" t="n">
-        <v>25.0994</v>
+        <v>60.7585</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>240.625</v>
+        <v>162.375</v>
       </c>
       <c r="P15" t="n">
         <v>20</v>
       </c>
       <c r="Q15" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="R15" t="n">
-        <v>2403</v>
+        <v>1622</v>
       </c>
       <c r="S15" t="n">
-        <v>2403</v>
+        <v>1622</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -4800,40 +4800,40 @@
         <v>2039</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0397</v>
+        <v>0.0181</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4184</v>
+        <v>0.3318</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4762</v>
+        <v>3.6955</v>
       </c>
       <c r="K16" t="n">
-        <v>7.9661</v>
+        <v>9.8942</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1586</v>
+        <v>0.0485</v>
       </c>
       <c r="M16" t="n">
-        <v>24.2254</v>
+        <v>61.9222</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>240</v>
+        <v>161.25</v>
       </c>
       <c r="P16" t="n">
         <v>20</v>
       </c>
       <c r="Q16" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="R16" t="n">
-        <v>2393</v>
+        <v>1599</v>
       </c>
       <c r="S16" t="n">
-        <v>2393</v>
+        <v>1599</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -4865,40 +4865,40 @@
         <v>2040</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0395</v>
+        <v>0.0235</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4611</v>
+        <v>0.3116</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5254</v>
+        <v>3.496</v>
       </c>
       <c r="K17" t="n">
-        <v>7.8761</v>
+        <v>15.2268</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1581</v>
+        <v>0.0634</v>
       </c>
       <c r="M17" t="n">
-        <v>24.3927</v>
+        <v>61.7769</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>240.125</v>
+        <v>162.125</v>
       </c>
       <c r="P17" t="n">
         <v>20</v>
       </c>
       <c r="Q17" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="R17" t="n">
-        <v>2412</v>
+        <v>1622</v>
       </c>
       <c r="S17" t="n">
-        <v>2412</v>
+        <v>1622</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -4930,40 +4930,40 @@
         <v>2041</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0377</v>
+        <v>0.0172</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6484</v>
+        <v>0.2846</v>
       </c>
       <c r="J18" t="n">
-        <v>2.566</v>
+        <v>3.7802</v>
       </c>
       <c r="K18" t="n">
-        <v>8.8969</v>
+        <v>12.5204</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1487</v>
+        <v>0.045</v>
       </c>
       <c r="M18" t="n">
-        <v>27.6099</v>
+        <v>65.2428</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>236.375</v>
+        <v>157.375</v>
       </c>
       <c r="P18" t="n">
         <v>20</v>
       </c>
       <c r="Q18" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="R18" t="n">
-        <v>2356</v>
+        <v>1568</v>
       </c>
       <c r="S18" t="n">
-        <v>2356</v>
+        <v>1568</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -4995,43 +4995,43 @@
         <v>2042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0313</v>
+        <v>0.0185</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3522</v>
+        <v>0.301</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5362</v>
+        <v>3.7414</v>
       </c>
       <c r="K19" t="n">
-        <v>8.7524</v>
+        <v>13.1652</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1256</v>
+        <v>0.0489</v>
       </c>
       <c r="M19" t="n">
-        <v>24.0636</v>
+        <v>64.10129999999999</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>240.5</v>
+        <v>158</v>
       </c>
       <c r="P19" t="n">
         <v>20</v>
       </c>
       <c r="Q19" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="R19" t="n">
-        <v>2427</v>
+        <v>1613</v>
       </c>
       <c r="S19" t="n">
-        <v>2427</v>
+        <v>1611</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -5060,43 +5060,43 @@
         <v>2043</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0422</v>
+        <v>0.0246</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4648</v>
+        <v>0.2924</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4562</v>
+        <v>3.6248</v>
       </c>
       <c r="K20" t="n">
-        <v>8.31</v>
+        <v>11.9285</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1743</v>
+        <v>0.0672</v>
       </c>
       <c r="M20" t="n">
-        <v>21.7546</v>
+        <v>62.002</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>248</v>
+        <v>163.25</v>
       </c>
       <c r="P20" t="n">
         <v>20</v>
       </c>
       <c r="Q20" t="n">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="R20" t="n">
-        <v>2452</v>
+        <v>1621</v>
       </c>
       <c r="S20" t="n">
-        <v>2452</v>
+        <v>1620</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -5125,40 +5125,40 @@
         <v>2044</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0362</v>
+        <v>0.0227</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4566</v>
+        <v>0.3427</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5472</v>
+        <v>3.5435</v>
       </c>
       <c r="K21" t="n">
-        <v>8.4499</v>
+        <v>11.5143</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1438</v>
+        <v>0.0616</v>
       </c>
       <c r="M21" t="n">
-        <v>25.1585</v>
+        <v>61.697</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>238.125</v>
+        <v>163</v>
       </c>
       <c r="P21" t="n">
         <v>20</v>
       </c>
       <c r="Q21" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="R21" t="n">
-        <v>2356</v>
+        <v>1601</v>
       </c>
       <c r="S21" t="n">
-        <v>2356</v>
+        <v>1601</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -5190,40 +5190,40 @@
         <v>2045</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0389</v>
+        <v>0.0194</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4979</v>
+        <v>0.3303</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4401</v>
+        <v>3.6093</v>
       </c>
       <c r="K22" t="n">
-        <v>8.029</v>
+        <v>11.2537</v>
       </c>
       <c r="L22" t="n">
-        <v>0.159</v>
+        <v>0.0524</v>
       </c>
       <c r="M22" t="n">
-        <v>22.9327</v>
+        <v>64.12050000000001</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>245.25</v>
+        <v>162.125</v>
       </c>
       <c r="P22" t="n">
         <v>20</v>
       </c>
       <c r="Q22" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="R22" t="n">
-        <v>2427</v>
+        <v>1592</v>
       </c>
       <c r="S22" t="n">
-        <v>2427</v>
+        <v>1592</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -5255,43 +5255,43 @@
         <v>2046</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0366</v>
+        <v>0.0221</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4437</v>
+        <v>0.3368</v>
       </c>
       <c r="J23" t="n">
-        <v>2.474</v>
+        <v>3.5674</v>
       </c>
       <c r="K23" t="n">
-        <v>7.4316</v>
+        <v>11.2051</v>
       </c>
       <c r="L23" t="n">
-        <v>0.149</v>
+        <v>0.06</v>
       </c>
       <c r="M23" t="n">
-        <v>23.0596</v>
+        <v>62.2006</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>244.25</v>
+        <v>163</v>
       </c>
       <c r="P23" t="n">
         <v>20</v>
       </c>
       <c r="Q23" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="R23" t="n">
-        <v>2427</v>
+        <v>1608</v>
       </c>
       <c r="S23" t="n">
-        <v>2426</v>
+        <v>1608</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -5320,40 +5320,40 @@
         <v>2047</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0444</v>
+        <v>0.0231</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4873</v>
+        <v>0.4045</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5021</v>
+        <v>3.5133</v>
       </c>
       <c r="K24" t="n">
-        <v>8.261200000000001</v>
+        <v>12.0427</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1807</v>
+        <v>0.0636</v>
       </c>
       <c r="M24" t="n">
-        <v>22.7923</v>
+        <v>60.6345</v>
       </c>
       <c r="N24" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>244.375</v>
+        <v>165.375</v>
       </c>
       <c r="P24" t="n">
         <v>20</v>
       </c>
       <c r="Q24" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="R24" t="n">
-        <v>2469</v>
+        <v>1647</v>
       </c>
       <c r="S24" t="n">
-        <v>2469</v>
+        <v>1647</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -5385,43 +5385,43 @@
         <v>2048</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0398</v>
+        <v>0.0201</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4747</v>
+        <v>0.3098</v>
       </c>
       <c r="J25" t="n">
-        <v>2.385</v>
+        <v>3.5951</v>
       </c>
       <c r="K25" t="n">
-        <v>8.831899999999999</v>
+        <v>12.5096</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1642</v>
+        <v>0.0547</v>
       </c>
       <c r="M25" t="n">
-        <v>23.7355</v>
+        <v>58.7719</v>
       </c>
       <c r="N25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>247.25</v>
+        <v>163.625</v>
       </c>
       <c r="P25" t="n">
         <v>20</v>
       </c>
       <c r="Q25" t="n">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="R25" t="n">
-        <v>2453</v>
+        <v>1615</v>
       </c>
       <c r="S25" t="n">
-        <v>2452</v>
+        <v>1615</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -5450,40 +5450,40 @@
         <v>2049</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0359</v>
+        <v>0.0197</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5151</v>
+        <v>0.3353</v>
       </c>
       <c r="J26" t="n">
-        <v>2.4988</v>
+        <v>3.7917</v>
       </c>
       <c r="K26" t="n">
-        <v>9.16</v>
+        <v>11.1807</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1449</v>
+        <v>0.0521</v>
       </c>
       <c r="M26" t="n">
-        <v>23.9434</v>
+        <v>63.6616</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>242.25</v>
+        <v>158.625</v>
       </c>
       <c r="P26" t="n">
         <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="R26" t="n">
-        <v>2415</v>
+        <v>1570</v>
       </c>
       <c r="S26" t="n">
-        <v>2415</v>
+        <v>1570</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -5515,43 +5515,43 @@
         <v>2050</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0356</v>
+        <v>0.0181</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4274</v>
+        <v>0.2725</v>
       </c>
       <c r="J27" t="n">
-        <v>2.5047</v>
+        <v>3.6648</v>
       </c>
       <c r="K27" t="n">
-        <v>7.0696</v>
+        <v>10.3058</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1444</v>
+        <v>0.0493</v>
       </c>
       <c r="M27" t="n">
-        <v>23.8069</v>
+        <v>63.5013</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>243.375</v>
+        <v>163.375</v>
       </c>
       <c r="P27" t="n">
         <v>20</v>
       </c>
       <c r="Q27" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="R27" t="n">
-        <v>2428</v>
+        <v>1620</v>
       </c>
       <c r="S27" t="n">
-        <v>2428</v>
+        <v>1619</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -5580,40 +5580,40 @@
         <v>2051</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0392</v>
+        <v>0.0227</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5206</v>
+        <v>0.3071</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4468</v>
+        <v>3.7502</v>
       </c>
       <c r="K28" t="n">
-        <v>8.320499999999999</v>
+        <v>12.2603</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1598</v>
+        <v>0.0576</v>
       </c>
       <c r="M28" t="n">
-        <v>24.7134</v>
+        <v>68.29340000000001</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>244.75</v>
+        <v>152.375</v>
       </c>
       <c r="P28" t="n">
         <v>20</v>
       </c>
       <c r="Q28" t="n">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="R28" t="n">
-        <v>2405</v>
+        <v>1534</v>
       </c>
       <c r="S28" t="n">
-        <v>2405</v>
+        <v>1534</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -5645,43 +5645,43 @@
         <v>2052</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0407</v>
+        <v>0.0213</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6313</v>
+        <v>0.3608</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4397</v>
+        <v>3.9399</v>
       </c>
       <c r="K29" t="n">
-        <v>7.8153</v>
+        <v>12.6178</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1684</v>
+        <v>0.0546</v>
       </c>
       <c r="M29" t="n">
-        <v>24.411</v>
+        <v>71.1341</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>247.875</v>
+        <v>153.625</v>
       </c>
       <c r="P29" t="n">
         <v>20</v>
       </c>
       <c r="Q29" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="R29" t="n">
-        <v>2403</v>
+        <v>1520</v>
       </c>
       <c r="S29" t="n">
-        <v>2402</v>
+        <v>1520</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5710,43 +5710,43 @@
         <v>2053</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0394</v>
+        <v>0.0214</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6871</v>
+        <v>0.2947</v>
       </c>
       <c r="J30" t="n">
-        <v>2.5941</v>
+        <v>3.7408</v>
       </c>
       <c r="K30" t="n">
-        <v>8.583600000000001</v>
+        <v>12.2318</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1537</v>
+        <v>0.0564</v>
       </c>
       <c r="M30" t="n">
-        <v>27.7735</v>
+        <v>66.31189999999999</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>233.625</v>
+        <v>158.125</v>
       </c>
       <c r="P30" t="n">
         <v>20</v>
       </c>
       <c r="Q30" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="R30" t="n">
-        <v>2354</v>
+        <v>1587</v>
       </c>
       <c r="S30" t="n">
-        <v>2352</v>
+        <v>1587</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5775,40 +5775,40 @@
         <v>2054</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0368</v>
+        <v>0.0176</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5471</v>
+        <v>0.2603</v>
       </c>
       <c r="J31" t="n">
-        <v>2.5261</v>
+        <v>3.7363</v>
       </c>
       <c r="K31" t="n">
-        <v>7.386</v>
+        <v>11.2857</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1448</v>
+        <v>0.0453</v>
       </c>
       <c r="M31" t="n">
-        <v>26.1386</v>
+        <v>65.2854</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>236.25</v>
+        <v>154.625</v>
       </c>
       <c r="P31" t="n">
         <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="R31" t="n">
-        <v>2344</v>
+        <v>1541</v>
       </c>
       <c r="S31" t="n">
-        <v>2344</v>
+        <v>1541</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -5843,40 +5843,40 @@
         <v>2025</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0382</v>
+        <v>0.0193</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4802</v>
+        <v>0.2917</v>
       </c>
       <c r="J32" t="n">
-        <v>2.2997</v>
+        <v>2.5926</v>
       </c>
       <c r="K32" t="n">
-        <v>5.4609</v>
+        <v>5.2368</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1537</v>
+        <v>0.0513</v>
       </c>
       <c r="M32" t="n">
-        <v>19.5947</v>
+        <v>25.6134</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>241.625</v>
+        <v>159.75</v>
       </c>
       <c r="P32" t="n">
-        <v>18.3396</v>
+        <v>13.3333</v>
       </c>
       <c r="Q32" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="R32" t="n">
-        <v>2408</v>
+        <v>1603</v>
       </c>
       <c r="S32" t="n">
-        <v>2408</v>
+        <v>1603</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -5911,40 +5911,40 @@
         <v>2026</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0326</v>
+        <v>0.0184</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3739</v>
+        <v>0.2699</v>
       </c>
       <c r="J33" t="n">
-        <v>2.2879</v>
+        <v>2.4838</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1414</v>
+        <v>5.2101</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1321</v>
+        <v>0.0486</v>
       </c>
       <c r="M33" t="n">
-        <v>18.3984</v>
+        <v>24.7556</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>243</v>
+        <v>158.625</v>
       </c>
       <c r="P33" t="n">
-        <v>18.271</v>
+        <v>13.1771</v>
       </c>
       <c r="Q33" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="R33" t="n">
-        <v>2416</v>
+        <v>1554</v>
       </c>
       <c r="S33" t="n">
-        <v>2416</v>
+        <v>1554</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -5979,43 +5979,43 @@
         <v>2027</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0358</v>
+        <v>0.0215</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4997</v>
+        <v>0.3026</v>
       </c>
       <c r="J34" t="n">
-        <v>2.32</v>
+        <v>2.5133</v>
       </c>
       <c r="K34" t="n">
-        <v>5.3303</v>
+        <v>5.1983</v>
       </c>
       <c r="L34" t="n">
-        <v>0.144</v>
+        <v>0.0564</v>
       </c>
       <c r="M34" t="n">
-        <v>18.8207</v>
+        <v>26.1431</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>241.5</v>
+        <v>157.75</v>
       </c>
       <c r="P34" t="n">
-        <v>18.5673</v>
+        <v>13.134</v>
       </c>
       <c r="Q34" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="R34" t="n">
-        <v>2387</v>
+        <v>1569</v>
       </c>
       <c r="S34" t="n">
-        <v>2386</v>
+        <v>1569</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -6047,40 +6047,40 @@
         <v>2028</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0369</v>
+        <v>0.0199</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4499</v>
+        <v>0.3041</v>
       </c>
       <c r="J35" t="n">
-        <v>2.2873</v>
+        <v>2.5469</v>
       </c>
       <c r="K35" t="n">
-        <v>5.1955</v>
+        <v>5.1114</v>
       </c>
       <c r="L35" t="n">
-        <v>0.1486</v>
+        <v>0.0526</v>
       </c>
       <c r="M35" t="n">
-        <v>19.082</v>
+        <v>25.0916</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>241.75</v>
+        <v>158.5</v>
       </c>
       <c r="P35" t="n">
-        <v>18.3905</v>
+        <v>13.1458</v>
       </c>
       <c r="Q35" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R35" t="n">
-        <v>2411</v>
+        <v>1618</v>
       </c>
       <c r="S35" t="n">
-        <v>2411</v>
+        <v>1618</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -6115,40 +6115,40 @@
         <v>2029</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0525</v>
+        <v>0.0215</v>
       </c>
       <c r="I36" t="n">
-        <v>2.1864</v>
+        <v>0.2768</v>
       </c>
       <c r="J36" t="n">
-        <v>2.3164</v>
+        <v>2.4416</v>
       </c>
       <c r="K36" t="n">
-        <v>5.1587</v>
+        <v>5.2033</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2144</v>
+        <v>0.0567</v>
       </c>
       <c r="M36" t="n">
-        <v>17.4653</v>
+        <v>25.7947</v>
       </c>
       <c r="N36" t="n">
-        <v>0.991</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>244.875</v>
+        <v>158.625</v>
       </c>
       <c r="P36" t="n">
-        <v>18.619</v>
+        <v>13.1753</v>
       </c>
       <c r="Q36" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="R36" t="n">
-        <v>2433</v>
+        <v>1597</v>
       </c>
       <c r="S36" t="n">
-        <v>2433</v>
+        <v>1597</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -6183,40 +6183,40 @@
         <v>2030</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0551</v>
+        <v>0.0227</v>
       </c>
       <c r="I37" t="n">
-        <v>2.831</v>
+        <v>0.3394</v>
       </c>
       <c r="J37" t="n">
-        <v>2.3129</v>
+        <v>2.531</v>
       </c>
       <c r="K37" t="n">
-        <v>5.6332</v>
+        <v>5.2798</v>
       </c>
       <c r="L37" t="n">
-        <v>0.223</v>
+        <v>0.0605</v>
       </c>
       <c r="M37" t="n">
-        <v>17.8352</v>
+        <v>25.1281</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9886</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>242.625</v>
+        <v>159.75</v>
       </c>
       <c r="P37" t="n">
-        <v>18.3585</v>
+        <v>13.3299</v>
       </c>
       <c r="Q37" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="R37" t="n">
-        <v>2406</v>
+        <v>1594</v>
       </c>
       <c r="S37" t="n">
-        <v>2406</v>
+        <v>1594</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -6251,40 +6251,40 @@
         <v>2031</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0411</v>
+        <v>0.0217</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5734</v>
+        <v>0.4276</v>
       </c>
       <c r="J38" t="n">
-        <v>2.3633</v>
+        <v>2.4769</v>
       </c>
       <c r="K38" t="n">
-        <v>6.5124</v>
+        <v>5.1474</v>
       </c>
       <c r="L38" t="n">
-        <v>0.1654</v>
+        <v>0.0591</v>
       </c>
       <c r="M38" t="n">
-        <v>19.0025</v>
+        <v>23.5669</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9943</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>241.25</v>
+        <v>163.75</v>
       </c>
       <c r="P38" t="n">
-        <v>18.5577</v>
+        <v>13.5521</v>
       </c>
       <c r="Q38" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="R38" t="n">
-        <v>2395</v>
+        <v>1613</v>
       </c>
       <c r="S38" t="n">
-        <v>2395</v>
+        <v>1613</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -6319,40 +6319,40 @@
         <v>2032</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0392</v>
+        <v>0.0192</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4577</v>
+        <v>0.2967</v>
       </c>
       <c r="J39" t="n">
-        <v>2.2678</v>
+        <v>2.4748</v>
       </c>
       <c r="K39" t="n">
-        <v>5.229</v>
+        <v>5.1443</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1594</v>
+        <v>0.0515</v>
       </c>
       <c r="M39" t="n">
-        <v>19.8554</v>
+        <v>23.434</v>
       </c>
       <c r="N39" t="n">
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>243.75</v>
+        <v>161.375</v>
       </c>
       <c r="P39" t="n">
-        <v>18.3962</v>
+        <v>13.3402</v>
       </c>
       <c r="Q39" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="R39" t="n">
-        <v>2426</v>
+        <v>1587</v>
       </c>
       <c r="S39" t="n">
-        <v>2426</v>
+        <v>1587</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -6387,40 +6387,40 @@
         <v>2033</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0447</v>
+        <v>0.0229</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5535</v>
+        <v>0.4036</v>
       </c>
       <c r="J40" t="n">
-        <v>2.2896</v>
+        <v>2.5192</v>
       </c>
       <c r="K40" t="n">
-        <v>5.2903</v>
+        <v>5.1997</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1794</v>
+        <v>0.0595</v>
       </c>
       <c r="M40" t="n">
-        <v>18.49</v>
+        <v>24.6484</v>
       </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>240.625</v>
+        <v>156</v>
       </c>
       <c r="P40" t="n">
-        <v>18.3396</v>
+        <v>12.8247</v>
       </c>
       <c r="Q40" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="R40" t="n">
-        <v>2435</v>
+        <v>1551</v>
       </c>
       <c r="S40" t="n">
-        <v>2435</v>
+        <v>1551</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -6455,40 +6455,40 @@
         <v>2034</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0334</v>
+        <v>0.0195</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4211</v>
+        <v>0.3849</v>
       </c>
       <c r="J41" t="n">
-        <v>2.2579</v>
+        <v>2.5123</v>
       </c>
       <c r="K41" t="n">
-        <v>5.3947</v>
+        <v>5.2201</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1327</v>
+        <v>0.0519</v>
       </c>
       <c r="M41" t="n">
-        <v>19.8715</v>
+        <v>25.7624</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>238.375</v>
+        <v>159.375</v>
       </c>
       <c r="P41" t="n">
-        <v>18.2692</v>
+        <v>13.2604</v>
       </c>
       <c r="Q41" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="R41" t="n">
-        <v>2357</v>
+        <v>1586</v>
       </c>
       <c r="S41" t="n">
-        <v>2357</v>
+        <v>1586</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -6523,40 +6523,40 @@
         <v>2035</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0395</v>
+        <v>0.0208</v>
       </c>
       <c r="I42" t="n">
-        <v>0.516</v>
+        <v>0.3232</v>
       </c>
       <c r="J42" t="n">
-        <v>2.2484</v>
+        <v>2.5167</v>
       </c>
       <c r="K42" t="n">
-        <v>5.1758</v>
+        <v>5.2392</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1631</v>
+        <v>0.0578</v>
       </c>
       <c r="M42" t="n">
-        <v>16.9567</v>
+        <v>24.3576</v>
       </c>
       <c r="N42" t="n">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>247.75</v>
+        <v>166.375</v>
       </c>
       <c r="P42" t="n">
-        <v>18.5943</v>
+        <v>13.7732</v>
       </c>
       <c r="Q42" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="R42" t="n">
-        <v>2425</v>
+        <v>1633</v>
       </c>
       <c r="S42" t="n">
-        <v>2425</v>
+        <v>1633</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -6591,40 +6591,40 @@
         <v>2036</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0374</v>
+        <v>0.0206</v>
       </c>
       <c r="I43" t="n">
-        <v>0.604</v>
+        <v>0.4187</v>
       </c>
       <c r="J43" t="n">
-        <v>2.2613</v>
+        <v>2.5591</v>
       </c>
       <c r="K43" t="n">
-        <v>5.1688</v>
+        <v>5.1053</v>
       </c>
       <c r="L43" t="n">
-        <v>0.153</v>
+        <v>0.0573</v>
       </c>
       <c r="M43" t="n">
-        <v>17.4729</v>
+        <v>24.2005</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9988</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>245.75</v>
+        <v>166.625</v>
       </c>
       <c r="P43" t="n">
-        <v>18.6132</v>
+        <v>13.8229</v>
       </c>
       <c r="Q43" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="R43" t="n">
-        <v>2423</v>
+        <v>1666</v>
       </c>
       <c r="S43" t="n">
-        <v>2423</v>
+        <v>1666</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -6659,40 +6659,40 @@
         <v>2037</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0339</v>
+        <v>0.0198</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5002</v>
+        <v>0.2942</v>
       </c>
       <c r="J44" t="n">
-        <v>2.2921</v>
+        <v>2.522</v>
       </c>
       <c r="K44" t="n">
-        <v>5.3323</v>
+        <v>5.1919</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1356</v>
+        <v>0.0541</v>
       </c>
       <c r="M44" t="n">
-        <v>19.5033</v>
+        <v>25.8519</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>239.75</v>
+        <v>163.875</v>
       </c>
       <c r="P44" t="n">
-        <v>18.2667</v>
+        <v>13.6667</v>
       </c>
       <c r="Q44" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R44" t="n">
-        <v>2374</v>
+        <v>1655</v>
       </c>
       <c r="S44" t="n">
-        <v>2374</v>
+        <v>1655</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -6727,43 +6727,43 @@
         <v>2038</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0379</v>
+        <v>0.0215</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4587</v>
+        <v>0.3105</v>
       </c>
       <c r="J45" t="n">
-        <v>2.2437</v>
+        <v>2.4868</v>
       </c>
       <c r="K45" t="n">
-        <v>5.4154</v>
+        <v>5.2434</v>
       </c>
       <c r="L45" t="n">
-        <v>0.1481</v>
+        <v>0.0586</v>
       </c>
       <c r="M45" t="n">
-        <v>17.7213</v>
+        <v>24.1728</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0.9988</v>
       </c>
       <c r="O45" t="n">
-        <v>234.25</v>
+        <v>163.125</v>
       </c>
       <c r="P45" t="n">
-        <v>17.8476</v>
+        <v>13.5625</v>
       </c>
       <c r="Q45" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R45" t="n">
-        <v>2334</v>
+        <v>1608</v>
       </c>
       <c r="S45" t="n">
-        <v>2334</v>
+        <v>1607</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -6795,40 +6795,40 @@
         <v>2039</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0407</v>
+        <v>0.0192</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4184</v>
+        <v>0.3262</v>
       </c>
       <c r="J46" t="n">
-        <v>2.3069</v>
+        <v>2.5423</v>
       </c>
       <c r="K46" t="n">
-        <v>5.3693</v>
+        <v>5.2444</v>
       </c>
       <c r="L46" t="n">
-        <v>0.169</v>
+        <v>0.0495</v>
       </c>
       <c r="M46" t="n">
-        <v>17.9642</v>
+        <v>24.2906</v>
       </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>249.25</v>
+        <v>154.5</v>
       </c>
       <c r="P46" t="n">
-        <v>18.8679</v>
+        <v>12.9167</v>
       </c>
       <c r="Q46" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="R46" t="n">
-        <v>2488</v>
+        <v>1547</v>
       </c>
       <c r="S46" t="n">
-        <v>2488</v>
+        <v>1547</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -6863,40 +6863,40 @@
         <v>2040</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0374</v>
+        <v>0.023</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4611</v>
+        <v>0.3116</v>
       </c>
       <c r="J47" t="n">
-        <v>2.3157</v>
+        <v>2.5113</v>
       </c>
       <c r="K47" t="n">
-        <v>5.3143</v>
+        <v>5.2027</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1492</v>
+        <v>0.0635</v>
       </c>
       <c r="M47" t="n">
-        <v>18.0211</v>
+        <v>25.6703</v>
       </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>239.5</v>
+        <v>165.875</v>
       </c>
       <c r="P47" t="n">
-        <v>18.3524</v>
+        <v>13.7113</v>
       </c>
       <c r="Q47" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="R47" t="n">
-        <v>2406</v>
+        <v>1644</v>
       </c>
       <c r="S47" t="n">
-        <v>2406</v>
+        <v>1644</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -6931,40 +6931,40 @@
         <v>2041</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0325</v>
+        <v>0.0169</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4245</v>
+        <v>0.3098</v>
       </c>
       <c r="J48" t="n">
-        <v>2.3233</v>
+        <v>2.525</v>
       </c>
       <c r="K48" t="n">
-        <v>5.3048</v>
+        <v>5.1312</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1253</v>
+        <v>0.0443</v>
       </c>
       <c r="M48" t="n">
-        <v>19.1042</v>
+        <v>23.7185</v>
       </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>231.25</v>
+        <v>157.125</v>
       </c>
       <c r="P48" t="n">
-        <v>17.8558</v>
+        <v>13</v>
       </c>
       <c r="Q48" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="R48" t="n">
-        <v>2314</v>
+        <v>1575</v>
       </c>
       <c r="S48" t="n">
-        <v>2314</v>
+        <v>1575</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -6999,40 +6999,40 @@
         <v>2042</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0339</v>
+        <v>0.018</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6352</v>
+        <v>0.2453</v>
       </c>
       <c r="J49" t="n">
-        <v>2.3171</v>
+        <v>2.5527</v>
       </c>
       <c r="K49" t="n">
-        <v>5.4741</v>
+        <v>5.3357</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1359</v>
+        <v>0.0479</v>
       </c>
       <c r="M49" t="n">
-        <v>19.1859</v>
+        <v>24.5229</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>240.875</v>
+        <v>159.875</v>
       </c>
       <c r="P49" t="n">
-        <v>18.3524</v>
+        <v>13.3438</v>
       </c>
       <c r="Q49" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R49" t="n">
-        <v>2394</v>
+        <v>1621</v>
       </c>
       <c r="S49" t="n">
-        <v>2394</v>
+        <v>1621</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -7067,40 +7067,40 @@
         <v>2043</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0388</v>
+        <v>0.0205</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4994</v>
+        <v>0.3048</v>
       </c>
       <c r="J50" t="n">
-        <v>2.2959</v>
+        <v>2.5447</v>
       </c>
       <c r="K50" t="n">
-        <v>5.2458</v>
+        <v>5.1504</v>
       </c>
       <c r="L50" t="n">
-        <v>0.1549</v>
+        <v>0.0559</v>
       </c>
       <c r="M50" t="n">
-        <v>18.2024</v>
+        <v>24.7117</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>239.5</v>
+        <v>163.5</v>
       </c>
       <c r="P50" t="n">
-        <v>18.1038</v>
+        <v>13.5464</v>
       </c>
       <c r="Q50" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="R50" t="n">
-        <v>2411</v>
+        <v>1600</v>
       </c>
       <c r="S50" t="n">
-        <v>2411</v>
+        <v>1600</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -7135,43 +7135,43 @@
         <v>2044</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0336</v>
+        <v>0.0214</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4315</v>
+        <v>0.4771</v>
       </c>
       <c r="J51" t="n">
-        <v>2.3493</v>
+        <v>2.5229</v>
       </c>
       <c r="K51" t="n">
-        <v>5.2707</v>
+        <v>5.3504</v>
       </c>
       <c r="L51" t="n">
-        <v>0.1328</v>
+        <v>0.0574</v>
       </c>
       <c r="M51" t="n">
-        <v>17.9904</v>
+        <v>24.0354</v>
       </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>237.125</v>
+        <v>160.875</v>
       </c>
       <c r="P51" t="n">
-        <v>18.2019</v>
+        <v>13.375</v>
       </c>
       <c r="Q51" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="R51" t="n">
-        <v>2392</v>
+        <v>1612</v>
       </c>
       <c r="S51" t="n">
-        <v>2391</v>
+        <v>1612</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -7203,40 +7203,40 @@
         <v>2045</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0623</v>
+        <v>0.019</v>
       </c>
       <c r="I52" t="n">
-        <v>2.9352</v>
+        <v>0.4384</v>
       </c>
       <c r="J52" t="n">
-        <v>2.2829</v>
+        <v>2.5328</v>
       </c>
       <c r="K52" t="n">
-        <v>5.2677</v>
+        <v>5.2217</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2582</v>
+        <v>0.0506</v>
       </c>
       <c r="M52" t="n">
-        <v>17.6714</v>
+        <v>24.2872</v>
       </c>
       <c r="N52" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>248.625</v>
+        <v>159.5</v>
       </c>
       <c r="P52" t="n">
-        <v>18.6226</v>
+        <v>13.2577</v>
       </c>
       <c r="Q52" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="R52" t="n">
-        <v>2428</v>
+        <v>1604</v>
       </c>
       <c r="S52" t="n">
-        <v>2428</v>
+        <v>1604</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -7271,40 +7271,40 @@
         <v>2046</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0525</v>
+        <v>0.0245</v>
       </c>
       <c r="I53" t="n">
-        <v>3.1994</v>
+        <v>0.4254</v>
       </c>
       <c r="J53" t="n">
-        <v>2.296</v>
+        <v>2.4288</v>
       </c>
       <c r="K53" t="n">
-        <v>5.7767</v>
+        <v>5.2264</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2098</v>
+        <v>0.0669</v>
       </c>
       <c r="M53" t="n">
-        <v>19.8551</v>
+        <v>24.7203</v>
       </c>
       <c r="N53" t="n">
-        <v>0.9892</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>239.875</v>
+        <v>163.875</v>
       </c>
       <c r="P53" t="n">
-        <v>18.5865</v>
+        <v>13.6289</v>
       </c>
       <c r="Q53" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="R53" t="n">
-        <v>2378</v>
+        <v>1631</v>
       </c>
       <c r="S53" t="n">
-        <v>2378</v>
+        <v>1631</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -7339,40 +7339,40 @@
         <v>2047</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0465</v>
+        <v>0.0204</v>
       </c>
       <c r="I54" t="n">
-        <v>1.719</v>
+        <v>0.3259</v>
       </c>
       <c r="J54" t="n">
-        <v>2.2891</v>
+        <v>2.5816</v>
       </c>
       <c r="K54" t="n">
-        <v>5.1844</v>
+        <v>5.2805</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1905</v>
+        <v>0.0539</v>
       </c>
       <c r="M54" t="n">
-        <v>16.7011</v>
+        <v>26.4486</v>
       </c>
       <c r="N54" t="n">
-        <v>0.9962</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>246</v>
+        <v>158.625</v>
       </c>
       <c r="P54" t="n">
-        <v>18.6132</v>
+        <v>13.2316</v>
       </c>
       <c r="Q54" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="R54" t="n">
-        <v>2501</v>
+        <v>1608</v>
       </c>
       <c r="S54" t="n">
-        <v>2501</v>
+        <v>1608</v>
       </c>
       <c r="T54" t="n">
         <v>0</v>
@@ -7407,40 +7407,40 @@
         <v>2048</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0389</v>
+        <v>0.0201</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3925</v>
+        <v>0.3312</v>
       </c>
       <c r="J55" t="n">
-        <v>2.2979</v>
+        <v>2.4916</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1675</v>
+        <v>5.1434</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1595</v>
+        <v>0.0544</v>
       </c>
       <c r="M55" t="n">
-        <v>19.9284</v>
+        <v>24.8542</v>
       </c>
       <c r="N55" t="n">
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>245.75</v>
+        <v>162</v>
       </c>
       <c r="P55" t="n">
-        <v>18.8173</v>
+        <v>13.4688</v>
       </c>
       <c r="Q55" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="R55" t="n">
-        <v>2436</v>
+        <v>1609</v>
       </c>
       <c r="S55" t="n">
-        <v>2436</v>
+        <v>1609</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -7475,40 +7475,40 @@
         <v>2049</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0332</v>
+        <v>0.0184</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5151</v>
+        <v>0.3051</v>
       </c>
       <c r="J56" t="n">
-        <v>2.3219</v>
+        <v>2.5505</v>
       </c>
       <c r="K56" t="n">
-        <v>5.1407</v>
+        <v>5.2178</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1336</v>
+        <v>0.0472</v>
       </c>
       <c r="M56" t="n">
-        <v>18.5343</v>
+        <v>25.0351</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>241.625</v>
+        <v>154.125</v>
       </c>
       <c r="P56" t="n">
-        <v>18.5673</v>
+        <v>12.9062</v>
       </c>
       <c r="Q56" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="R56" t="n">
-        <v>2422</v>
+        <v>1538</v>
       </c>
       <c r="S56" t="n">
-        <v>2422</v>
+        <v>1538</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -7543,43 +7543,43 @@
         <v>2050</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0354</v>
+        <v>0.0176</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4857</v>
+        <v>0.3234</v>
       </c>
       <c r="J57" t="n">
-        <v>2.2899</v>
+        <v>2.5982</v>
       </c>
       <c r="K57" t="n">
-        <v>5.1455</v>
+        <v>5.2476</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1428</v>
+        <v>0.0482</v>
       </c>
       <c r="M57" t="n">
-        <v>18.8989</v>
+        <v>23.8867</v>
       </c>
       <c r="N57" t="n">
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>241.75</v>
+        <v>164.25</v>
       </c>
       <c r="P57" t="n">
-        <v>18.4</v>
+        <v>13.6458</v>
       </c>
       <c r="Q57" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R57" t="n">
-        <v>2407</v>
+        <v>1622</v>
       </c>
       <c r="S57" t="n">
-        <v>2406</v>
+        <v>1622</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -7611,40 +7611,40 @@
         <v>2051</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0414</v>
+        <v>0.0196</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9442</v>
+        <v>0.3291</v>
       </c>
       <c r="J58" t="n">
-        <v>2.2479</v>
+        <v>2.5392</v>
       </c>
       <c r="K58" t="n">
-        <v>5.3126</v>
+        <v>5.2139</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1676</v>
+        <v>0.0501</v>
       </c>
       <c r="M58" t="n">
-        <v>17.9594</v>
+        <v>23.8168</v>
       </c>
       <c r="N58" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>242.875</v>
+        <v>153.375</v>
       </c>
       <c r="P58" t="n">
-        <v>18.2056</v>
+        <v>12.8041</v>
       </c>
       <c r="Q58" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="R58" t="n">
-        <v>2370</v>
+        <v>1550</v>
       </c>
       <c r="S58" t="n">
-        <v>2370</v>
+        <v>1550</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -7679,40 +7679,40 @@
         <v>2052</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0417</v>
+        <v>0.0223</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6313</v>
+        <v>0.3548</v>
       </c>
       <c r="J59" t="n">
-        <v>2.3151</v>
+        <v>2.5498</v>
       </c>
       <c r="K59" t="n">
-        <v>5.284</v>
+        <v>5.1896</v>
       </c>
       <c r="L59" t="n">
-        <v>0.1688</v>
+        <v>0.0579</v>
       </c>
       <c r="M59" t="n">
-        <v>16.4997</v>
+        <v>24.633</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>243.125</v>
+        <v>155.375</v>
       </c>
       <c r="P59" t="n">
-        <v>18.3019</v>
+        <v>13.0417</v>
       </c>
       <c r="Q59" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="R59" t="n">
-        <v>2411</v>
+        <v>1548</v>
       </c>
       <c r="S59" t="n">
-        <v>2411</v>
+        <v>1548</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -7747,40 +7747,40 @@
         <v>2053</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0357</v>
+        <v>0.0213</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.2645</v>
       </c>
       <c r="J60" t="n">
-        <v>2.3208</v>
+        <v>2.5114</v>
       </c>
       <c r="K60" t="n">
-        <v>5.1566</v>
+        <v>5.2382</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1405</v>
+        <v>0.0572</v>
       </c>
       <c r="M60" t="n">
-        <v>18.3342</v>
+        <v>25.1745</v>
       </c>
       <c r="N60" t="n">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>236.375</v>
+        <v>161.25</v>
       </c>
       <c r="P60" t="n">
-        <v>18.1538</v>
+        <v>13.4021</v>
       </c>
       <c r="Q60" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="R60" t="n">
-        <v>2401</v>
+        <v>1626</v>
       </c>
       <c r="S60" t="n">
-        <v>2401</v>
+        <v>1626</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -7815,40 +7815,40 @@
         <v>2054</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0396</v>
+        <v>0.0174</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4438</v>
+        <v>0.225</v>
       </c>
       <c r="J61" t="n">
-        <v>2.2826</v>
+        <v>2.5493</v>
       </c>
       <c r="K61" t="n">
-        <v>5.3258</v>
+        <v>5.1465</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1607</v>
+        <v>0.0439</v>
       </c>
       <c r="M61" t="n">
-        <v>17.6422</v>
+        <v>24.7297</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>243.5</v>
+        <v>151.875</v>
       </c>
       <c r="P61" t="n">
-        <v>18.4476</v>
+        <v>12.6979</v>
       </c>
       <c r="Q61" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R61" t="n">
-        <v>2413</v>
+        <v>1522</v>
       </c>
       <c r="S61" t="n">
-        <v>2413</v>
+        <v>1522</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -7880,43 +7880,43 @@
         <v>2025</v>
       </c>
       <c r="H62" t="n">
-        <v>0.022</v>
+        <v>0.0069</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3007</v>
+        <v>0.1909</v>
       </c>
       <c r="J62" t="n">
-        <v>3.3533</v>
+        <v>7.4822</v>
       </c>
       <c r="K62" t="n">
-        <v>11.9306</v>
+        <v>21.1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0641</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>52.6654</v>
+        <v>175.2573</v>
       </c>
       <c r="N62" t="n">
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>175.125</v>
+        <v>79</v>
       </c>
       <c r="P62" t="n">
         <v>20</v>
       </c>
       <c r="Q62" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="R62" t="n">
-        <v>1768</v>
+        <v>804</v>
       </c>
       <c r="S62" t="n">
-        <v>1767</v>
+        <v>804</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7945,40 +7945,40 @@
         <v>2026</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0233</v>
+        <v>0.0078</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3346</v>
+        <v>0.233</v>
       </c>
       <c r="J63" t="n">
-        <v>3.2436</v>
+        <v>7.2869</v>
       </c>
       <c r="K63" t="n">
-        <v>9.4413</v>
+        <v>21.241</v>
       </c>
       <c r="L63" t="n">
-        <v>0.0698</v>
+        <v>0.0101</v>
       </c>
       <c r="M63" t="n">
-        <v>50.6129</v>
+        <v>179.1628</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>179.5</v>
+        <v>78</v>
       </c>
       <c r="P63" t="n">
         <v>20</v>
       </c>
       <c r="Q63" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="R63" t="n">
-        <v>1783</v>
+        <v>781</v>
       </c>
       <c r="S63" t="n">
-        <v>1783</v>
+        <v>781</v>
       </c>
       <c r="T63" t="n">
         <v>0</v>
@@ -8010,40 +8010,40 @@
         <v>2027</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0224</v>
+        <v>0.0077</v>
       </c>
       <c r="I64" t="n">
-        <v>0.432</v>
+        <v>0.1693</v>
       </c>
       <c r="J64" t="n">
-        <v>3.3545</v>
+        <v>7.4983</v>
       </c>
       <c r="K64" t="n">
-        <v>11.1536</v>
+        <v>20.1457</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0646</v>
+        <v>0.0102</v>
       </c>
       <c r="M64" t="n">
-        <v>53.2034</v>
+        <v>177.4926</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>173.125</v>
+        <v>79.125</v>
       </c>
       <c r="P64" t="n">
         <v>20</v>
       </c>
       <c r="Q64" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="R64" t="n">
-        <v>1749</v>
+        <v>811</v>
       </c>
       <c r="S64" t="n">
-        <v>1749</v>
+        <v>811</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -8075,40 +8075,40 @@
         <v>2028</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0274</v>
+        <v>0.0075</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4046</v>
+        <v>0.2223</v>
       </c>
       <c r="J65" t="n">
-        <v>3.3175</v>
+        <v>7.4893</v>
       </c>
       <c r="K65" t="n">
-        <v>9.470599999999999</v>
+        <v>22.846</v>
       </c>
       <c r="L65" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0095</v>
       </c>
       <c r="M65" t="n">
-        <v>51.94</v>
+        <v>186.2895</v>
       </c>
       <c r="N65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>178.625</v>
+        <v>76.25</v>
       </c>
       <c r="P65" t="n">
         <v>20</v>
       </c>
       <c r="Q65" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="R65" t="n">
-        <v>1783</v>
+        <v>759</v>
       </c>
       <c r="S65" t="n">
-        <v>1783</v>
+        <v>759</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -8140,40 +8140,40 @@
         <v>2029</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0255</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3363</v>
+        <v>0.1676</v>
       </c>
       <c r="J66" t="n">
-        <v>3.1676</v>
+        <v>7.1541</v>
       </c>
       <c r="K66" t="n">
-        <v>9.2011</v>
+        <v>21.3846</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0785</v>
+        <v>0.0112</v>
       </c>
       <c r="M66" t="n">
-        <v>47.9435</v>
+        <v>171.8975</v>
       </c>
       <c r="N66" t="n">
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>184.875</v>
+        <v>82</v>
       </c>
       <c r="P66" t="n">
         <v>20</v>
       </c>
       <c r="Q66" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="R66" t="n">
-        <v>1827</v>
+        <v>804</v>
       </c>
       <c r="S66" t="n">
-        <v>1827</v>
+        <v>804</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
@@ -8205,40 +8205,40 @@
         <v>2030</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0255</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4562</v>
+        <v>0.264</v>
       </c>
       <c r="J67" t="n">
-        <v>3.4417</v>
+        <v>7.9255</v>
       </c>
       <c r="K67" t="n">
-        <v>14.4137</v>
+        <v>26.6053</v>
       </c>
       <c r="L67" t="n">
-        <v>0.0733</v>
+        <v>0.0123</v>
       </c>
       <c r="M67" t="n">
-        <v>54.4204</v>
+        <v>186.6431</v>
       </c>
       <c r="N67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>173.125</v>
+        <v>74.375</v>
       </c>
       <c r="P67" t="n">
         <v>20</v>
       </c>
       <c r="Q67" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="R67" t="n">
-        <v>1718</v>
+        <v>749</v>
       </c>
       <c r="S67" t="n">
-        <v>1718</v>
+        <v>749</v>
       </c>
       <c r="T67" t="n">
         <v>0</v>
@@ -8270,40 +8270,40 @@
         <v>2031</v>
       </c>
       <c r="H68" t="n">
-        <v>0.021</v>
+        <v>0.0077</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3055</v>
+        <v>0.1518</v>
       </c>
       <c r="J68" t="n">
-        <v>3.3729</v>
+        <v>7.2801</v>
       </c>
       <c r="K68" t="n">
-        <v>12.227</v>
+        <v>21.5849</v>
       </c>
       <c r="L68" t="n">
-        <v>0.0612</v>
+        <v>0.0101</v>
       </c>
       <c r="M68" t="n">
-        <v>52.3162</v>
+        <v>177.7305</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>174.625</v>
+        <v>79.25</v>
       </c>
       <c r="P68" t="n">
         <v>20</v>
       </c>
       <c r="Q68" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="R68" t="n">
-        <v>1767</v>
+        <v>783</v>
       </c>
       <c r="S68" t="n">
-        <v>1767</v>
+        <v>783</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
@@ -8335,40 +8335,40 @@
         <v>2032</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0249</v>
+        <v>0.007</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5891</v>
+        <v>0.1377</v>
       </c>
       <c r="J69" t="n">
-        <v>3.4327</v>
+        <v>7.8197</v>
       </c>
       <c r="K69" t="n">
-        <v>10.1194</v>
+        <v>21.9253</v>
       </c>
       <c r="L69" t="n">
-        <v>0.0723</v>
+        <v>0.0086</v>
       </c>
       <c r="M69" t="n">
-        <v>51.2641</v>
+        <v>186.8126</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>174.625</v>
+        <v>73.5</v>
       </c>
       <c r="P69" t="n">
         <v>20</v>
       </c>
       <c r="Q69" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="R69" t="n">
-        <v>1743</v>
+        <v>746</v>
       </c>
       <c r="S69" t="n">
-        <v>1743</v>
+        <v>746</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
@@ -8400,43 +8400,43 @@
         <v>2033</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0304</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5536</v>
+        <v>0.2005</v>
       </c>
       <c r="J70" t="n">
-        <v>3.22</v>
+        <v>6.7384</v>
       </c>
       <c r="K70" t="n">
-        <v>11.4581</v>
+        <v>18.6015</v>
       </c>
       <c r="L70" t="n">
-        <v>0.091</v>
+        <v>0.0133</v>
       </c>
       <c r="M70" t="n">
-        <v>48.2922</v>
+        <v>162.5098</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>179.5</v>
+        <v>85.5</v>
       </c>
       <c r="P70" t="n">
         <v>20</v>
       </c>
       <c r="Q70" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="R70" t="n">
-        <v>1805</v>
+        <v>847</v>
       </c>
       <c r="S70" t="n">
-        <v>1805</v>
+        <v>846</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -8465,40 +8465,40 @@
         <v>2034</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0247</v>
+        <v>0.007</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3127</v>
+        <v>0.217</v>
       </c>
       <c r="J71" t="n">
-        <v>3.2634</v>
+        <v>7.7223</v>
       </c>
       <c r="K71" t="n">
-        <v>10.9926</v>
+        <v>25.5573</v>
       </c>
       <c r="L71" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>53.7093</v>
+        <v>191.9285</v>
       </c>
       <c r="N71" t="n">
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>177.875</v>
+        <v>74.375</v>
       </c>
       <c r="P71" t="n">
         <v>20</v>
       </c>
       <c r="Q71" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="R71" t="n">
-        <v>1766</v>
+        <v>760</v>
       </c>
       <c r="S71" t="n">
-        <v>1766</v>
+        <v>760</v>
       </c>
       <c r="T71" t="n">
         <v>0</v>
@@ -8530,40 +8530,40 @@
         <v>2035</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0257</v>
+        <v>0.0068</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3518</v>
+        <v>0.1817</v>
       </c>
       <c r="J72" t="n">
-        <v>3.1968</v>
+        <v>7.6442</v>
       </c>
       <c r="K72" t="n">
-        <v>10.48</v>
+        <v>22.8651</v>
       </c>
       <c r="L72" t="n">
-        <v>0.0804</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>47.5011</v>
+        <v>179.4544</v>
       </c>
       <c r="N72" t="n">
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>187.5</v>
+        <v>79.25</v>
       </c>
       <c r="P72" t="n">
         <v>20</v>
       </c>
       <c r="Q72" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="R72" t="n">
-        <v>1847</v>
+        <v>782</v>
       </c>
       <c r="S72" t="n">
-        <v>1847</v>
+        <v>782</v>
       </c>
       <c r="T72" t="n">
         <v>0</v>
@@ -8595,40 +8595,40 @@
         <v>2036</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0226</v>
+        <v>0.008</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4292</v>
+        <v>0.2266</v>
       </c>
       <c r="J73" t="n">
-        <v>3.3248</v>
+        <v>7.3327</v>
       </c>
       <c r="K73" t="n">
-        <v>11.5999</v>
+        <v>19.5929</v>
       </c>
       <c r="L73" t="n">
-        <v>0.067</v>
+        <v>0.0106</v>
       </c>
       <c r="M73" t="n">
-        <v>51.9907</v>
+        <v>175.0841</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>177.375</v>
+        <v>79.5</v>
       </c>
       <c r="P73" t="n">
         <v>20</v>
       </c>
       <c r="Q73" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R73" t="n">
-        <v>1783</v>
+        <v>798</v>
       </c>
       <c r="S73" t="n">
-        <v>1783</v>
+        <v>798</v>
       </c>
       <c r="T73" t="n">
         <v>0</v>
@@ -8660,40 +8660,40 @@
         <v>2037</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0215</v>
+        <v>0.0081</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2872</v>
+        <v>0.2328</v>
       </c>
       <c r="J74" t="n">
-        <v>3.2664</v>
+        <v>6.9438</v>
       </c>
       <c r="K74" t="n">
-        <v>9.3294</v>
+        <v>19.5407</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0639</v>
+        <v>0.0105</v>
       </c>
       <c r="M74" t="n">
-        <v>49.324</v>
+        <v>177.97</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>178.625</v>
+        <v>78.5</v>
       </c>
       <c r="P74" t="n">
         <v>20</v>
       </c>
       <c r="Q74" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R74" t="n">
-        <v>1794</v>
+        <v>791</v>
       </c>
       <c r="S74" t="n">
-        <v>1794</v>
+        <v>791</v>
       </c>
       <c r="T74" t="n">
         <v>0</v>
@@ -8725,40 +8725,40 @@
         <v>2038</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0254</v>
+        <v>0.0109</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4164</v>
+        <v>0.3535</v>
       </c>
       <c r="J75" t="n">
-        <v>3.2983</v>
+        <v>7.3202</v>
       </c>
       <c r="K75" t="n">
-        <v>10.6217</v>
+        <v>19.8289</v>
       </c>
       <c r="L75" t="n">
-        <v>0.0755</v>
+        <v>0.0149</v>
       </c>
       <c r="M75" t="n">
-        <v>48.6659</v>
+        <v>169.1277</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>178.5</v>
+        <v>82</v>
       </c>
       <c r="P75" t="n">
         <v>20</v>
       </c>
       <c r="Q75" t="n">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="R75" t="n">
-        <v>1790</v>
+        <v>823</v>
       </c>
       <c r="S75" t="n">
-        <v>1790</v>
+        <v>823</v>
       </c>
       <c r="T75" t="n">
         <v>0</v>
@@ -8790,40 +8790,40 @@
         <v>2039</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0219</v>
+        <v>0.0089</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2702</v>
+        <v>0.2506</v>
       </c>
       <c r="J76" t="n">
-        <v>3.3068</v>
+        <v>7.2938</v>
       </c>
       <c r="K76" t="n">
-        <v>9.3817</v>
+        <v>22.193</v>
       </c>
       <c r="L76" t="n">
-        <v>0.066</v>
+        <v>0.0116</v>
       </c>
       <c r="M76" t="n">
-        <v>50.6835</v>
+        <v>180.1551</v>
       </c>
       <c r="N76" t="n">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>181.125</v>
+        <v>78.5</v>
       </c>
       <c r="P76" t="n">
         <v>20</v>
       </c>
       <c r="Q76" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="R76" t="n">
-        <v>1804</v>
+        <v>772</v>
       </c>
       <c r="S76" t="n">
-        <v>1804</v>
+        <v>772</v>
       </c>
       <c r="T76" t="n">
         <v>0</v>
@@ -8855,40 +8855,40 @@
         <v>2040</v>
       </c>
       <c r="H77" t="n">
-        <v>0.03</v>
+        <v>0.0076</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4966</v>
+        <v>0.1654</v>
       </c>
       <c r="J77" t="n">
-        <v>3.1575</v>
+        <v>7.1725</v>
       </c>
       <c r="K77" t="n">
-        <v>9.8749</v>
+        <v>23.2246</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0929</v>
+        <v>0.0103</v>
       </c>
       <c r="M77" t="n">
-        <v>46.5269</v>
+        <v>167.6844</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>185.875</v>
+        <v>81.25</v>
       </c>
       <c r="P77" t="n">
         <v>20</v>
       </c>
       <c r="Q77" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="R77" t="n">
-        <v>1860</v>
+        <v>798</v>
       </c>
       <c r="S77" t="n">
-        <v>1860</v>
+        <v>798</v>
       </c>
       <c r="T77" t="n">
         <v>0</v>
@@ -8920,40 +8920,40 @@
         <v>2041</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0213</v>
+        <v>0.0044</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3026</v>
+        <v>0.1696</v>
       </c>
       <c r="J78" t="n">
-        <v>3.3435</v>
+        <v>8.0633</v>
       </c>
       <c r="K78" t="n">
-        <v>11.1433</v>
+        <v>22.6489</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0633</v>
+        <v>0.0054</v>
       </c>
       <c r="M78" t="n">
-        <v>51.0238</v>
+        <v>187.1703</v>
       </c>
       <c r="N78" t="n">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>178.5</v>
+        <v>73.625</v>
       </c>
       <c r="P78" t="n">
         <v>20</v>
       </c>
       <c r="Q78" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="R78" t="n">
-        <v>1772</v>
+        <v>746</v>
       </c>
       <c r="S78" t="n">
-        <v>1772</v>
+        <v>746</v>
       </c>
       <c r="T78" t="n">
         <v>0</v>
@@ -8985,40 +8985,40 @@
         <v>2042</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0257</v>
+        <v>0.0076</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5041</v>
+        <v>0.223</v>
       </c>
       <c r="J79" t="n">
-        <v>3.3116</v>
+        <v>7.6179</v>
       </c>
       <c r="K79" t="n">
-        <v>11.5963</v>
+        <v>23.685</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0781</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>49.1567</v>
+        <v>172.3697</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>182.375</v>
+        <v>77.625</v>
       </c>
       <c r="P79" t="n">
         <v>20</v>
       </c>
       <c r="Q79" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="R79" t="n">
-        <v>1845</v>
+        <v>796</v>
       </c>
       <c r="S79" t="n">
-        <v>1845</v>
+        <v>796</v>
       </c>
       <c r="T79" t="n">
         <v>0</v>
@@ -9050,40 +9050,40 @@
         <v>2043</v>
       </c>
       <c r="H80" t="n">
-        <v>0.027</v>
+        <v>0.0107</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3647</v>
+        <v>0.2664</v>
       </c>
       <c r="J80" t="n">
-        <v>3.1496</v>
+        <v>7.7599</v>
       </c>
       <c r="K80" t="n">
-        <v>10.6806</v>
+        <v>23.0627</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0837</v>
+        <v>0.0132</v>
       </c>
       <c r="M80" t="n">
-        <v>46.7005</v>
+        <v>182.7514</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>186.25</v>
+        <v>74.5</v>
       </c>
       <c r="P80" t="n">
         <v>20</v>
       </c>
       <c r="Q80" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="R80" t="n">
-        <v>1851</v>
+        <v>768</v>
       </c>
       <c r="S80" t="n">
-        <v>1851</v>
+        <v>768</v>
       </c>
       <c r="T80" t="n">
         <v>0</v>
@@ -9115,40 +9115,40 @@
         <v>2044</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0268</v>
+        <v>0.0095</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4194</v>
+        <v>0.2956</v>
       </c>
       <c r="J81" t="n">
-        <v>3.4388</v>
+        <v>7.5993</v>
       </c>
       <c r="K81" t="n">
-        <v>10.3496</v>
+        <v>24.3245</v>
       </c>
       <c r="L81" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0125</v>
       </c>
       <c r="M81" t="n">
-        <v>51.2148</v>
+        <v>177.089</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>175.375</v>
+        <v>79</v>
       </c>
       <c r="P81" t="n">
         <v>20</v>
       </c>
       <c r="Q81" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="R81" t="n">
-        <v>1747</v>
+        <v>793</v>
       </c>
       <c r="S81" t="n">
-        <v>1747</v>
+        <v>793</v>
       </c>
       <c r="T81" t="n">
         <v>0</v>
@@ -9180,40 +9180,40 @@
         <v>2045</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0252</v>
+        <v>0.0058</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3723</v>
+        <v>0.1586</v>
       </c>
       <c r="J82" t="n">
-        <v>3.2777</v>
+        <v>7.5368</v>
       </c>
       <c r="K82" t="n">
-        <v>9.937900000000001</v>
+        <v>21.1531</v>
       </c>
       <c r="L82" t="n">
-        <v>0.0761</v>
+        <v>0.0073</v>
       </c>
       <c r="M82" t="n">
-        <v>50.595</v>
+        <v>190.6644</v>
       </c>
       <c r="N82" t="n">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>181.125</v>
+        <v>75.75</v>
       </c>
       <c r="P82" t="n">
         <v>20</v>
       </c>
       <c r="Q82" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="R82" t="n">
-        <v>1783</v>
+        <v>765</v>
       </c>
       <c r="S82" t="n">
-        <v>1783</v>
+        <v>765</v>
       </c>
       <c r="T82" t="n">
         <v>0</v>
@@ -9245,40 +9245,40 @@
         <v>2046</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0252</v>
+        <v>0.0103</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4509</v>
+        <v>0.3278</v>
       </c>
       <c r="J83" t="n">
-        <v>3.1831</v>
+        <v>6.836</v>
       </c>
       <c r="K83" t="n">
-        <v>9.9727</v>
+        <v>21.1442</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0776</v>
+        <v>0.0134</v>
       </c>
       <c r="M83" t="n">
-        <v>49.1756</v>
+        <v>182.2685</v>
       </c>
       <c r="N83" t="n">
         <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>184.375</v>
+        <v>78.125</v>
       </c>
       <c r="P83" t="n">
         <v>20</v>
       </c>
       <c r="Q83" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="R83" t="n">
-        <v>1820</v>
+        <v>785</v>
       </c>
       <c r="S83" t="n">
-        <v>1820</v>
+        <v>785</v>
       </c>
       <c r="T83" t="n">
         <v>0</v>
@@ -9310,40 +9310,40 @@
         <v>2047</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0283</v>
+        <v>0.0103</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3992</v>
+        <v>0.3089</v>
       </c>
       <c r="J84" t="n">
-        <v>3.1656</v>
+        <v>6.4702</v>
       </c>
       <c r="K84" t="n">
-        <v>10.7101</v>
+        <v>19.617</v>
       </c>
       <c r="L84" t="n">
-        <v>0.0871</v>
+        <v>0.0148</v>
       </c>
       <c r="M84" t="n">
-        <v>48.1536</v>
+        <v>165.7341</v>
       </c>
       <c r="N84" t="n">
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>185</v>
+        <v>85.625</v>
       </c>
       <c r="P84" t="n">
         <v>20</v>
       </c>
       <c r="Q84" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="R84" t="n">
-        <v>1846</v>
+        <v>858</v>
       </c>
       <c r="S84" t="n">
-        <v>1846</v>
+        <v>858</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
@@ -9375,43 +9375,43 @@
         <v>2048</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0243</v>
+        <v>0.0069</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3206</v>
+        <v>0.1445</v>
       </c>
       <c r="J85" t="n">
-        <v>3.2418</v>
+        <v>7.2786</v>
       </c>
       <c r="K85" t="n">
-        <v>11.085</v>
+        <v>24.1316</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0737</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="M85" t="n">
-        <v>47.4292</v>
+        <v>173.4791</v>
       </c>
       <c r="N85" t="n">
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>181</v>
+        <v>80.625</v>
       </c>
       <c r="P85" t="n">
         <v>20</v>
       </c>
       <c r="Q85" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="R85" t="n">
-        <v>1793</v>
+        <v>787</v>
       </c>
       <c r="S85" t="n">
-        <v>1791</v>
+        <v>787</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -9440,40 +9440,40 @@
         <v>2049</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0223</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>0.313</v>
+        <v>0.2591</v>
       </c>
       <c r="J86" t="n">
-        <v>3.3842</v>
+        <v>7.3551</v>
       </c>
       <c r="K86" t="n">
-        <v>10.8717</v>
+        <v>22.9133</v>
       </c>
       <c r="L86" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0115</v>
       </c>
       <c r="M86" t="n">
-        <v>52.1045</v>
+        <v>178.8694</v>
       </c>
       <c r="N86" t="n">
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>175.375</v>
+        <v>78.875</v>
       </c>
       <c r="P86" t="n">
         <v>20</v>
       </c>
       <c r="Q86" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="R86" t="n">
-        <v>1743</v>
+        <v>778</v>
       </c>
       <c r="S86" t="n">
-        <v>1743</v>
+        <v>778</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
@@ -9505,40 +9505,40 @@
         <v>2050</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0208</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2832</v>
+        <v>0.21</v>
       </c>
       <c r="J87" t="n">
-        <v>3.1582</v>
+        <v>7.1942</v>
       </c>
       <c r="K87" t="n">
-        <v>9.1637</v>
+        <v>22.1846</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0643</v>
+        <v>0.0122</v>
       </c>
       <c r="M87" t="n">
-        <v>48.5622</v>
+        <v>174.558</v>
       </c>
       <c r="N87" t="n">
         <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>185.125</v>
+        <v>81.625</v>
       </c>
       <c r="P87" t="n">
         <v>20</v>
       </c>
       <c r="Q87" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="R87" t="n">
-        <v>1836</v>
+        <v>817</v>
       </c>
       <c r="S87" t="n">
-        <v>1836</v>
+        <v>817</v>
       </c>
       <c r="T87" t="n">
         <v>0</v>
@@ -9570,40 +9570,40 @@
         <v>2051</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0247</v>
+        <v>0.0127</v>
       </c>
       <c r="I88" t="n">
-        <v>0.303</v>
+        <v>0.2711</v>
       </c>
       <c r="J88" t="n">
-        <v>3.3874</v>
+        <v>7.3542</v>
       </c>
       <c r="K88" t="n">
-        <v>10.9077</v>
+        <v>24.2053</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0713</v>
+        <v>0.0162</v>
       </c>
       <c r="M88" t="n">
-        <v>55.1645</v>
+        <v>187.4395</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>173.375</v>
+        <v>76.5</v>
       </c>
       <c r="P88" t="n">
         <v>20</v>
       </c>
       <c r="Q88" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="R88" t="n">
-        <v>1725</v>
+        <v>764</v>
       </c>
       <c r="S88" t="n">
-        <v>1725</v>
+        <v>764</v>
       </c>
       <c r="T88" t="n">
         <v>0</v>
@@ -9635,40 +9635,40 @@
         <v>2052</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0237</v>
+        <v>0.0092</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3833</v>
+        <v>0.2727</v>
       </c>
       <c r="J89" t="n">
-        <v>3.3719</v>
+        <v>7.9272</v>
       </c>
       <c r="K89" t="n">
-        <v>10.1249</v>
+        <v>25.1177</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0711</v>
+        <v>0.0111</v>
       </c>
       <c r="M89" t="n">
-        <v>53.2943</v>
+        <v>198.8144</v>
       </c>
       <c r="N89" t="n">
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>179.875</v>
+        <v>72.5</v>
       </c>
       <c r="P89" t="n">
         <v>20</v>
       </c>
       <c r="Q89" t="n">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="R89" t="n">
-        <v>1759</v>
+        <v>727</v>
       </c>
       <c r="S89" t="n">
-        <v>1759</v>
+        <v>727</v>
       </c>
       <c r="T89" t="n">
         <v>0</v>
@@ -9700,40 +9700,40 @@
         <v>2053</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0238</v>
+        <v>0.0092</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3483</v>
+        <v>0.1872</v>
       </c>
       <c r="J90" t="n">
-        <v>3.4068</v>
+        <v>7.3227</v>
       </c>
       <c r="K90" t="n">
-        <v>11.3588</v>
+        <v>22.3179</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0688</v>
+        <v>0.0121</v>
       </c>
       <c r="M90" t="n">
-        <v>52.4967</v>
+        <v>177.9653</v>
       </c>
       <c r="N90" t="n">
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>173.5</v>
+        <v>78.875</v>
       </c>
       <c r="P90" t="n">
         <v>20</v>
       </c>
       <c r="Q90" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="R90" t="n">
-        <v>1761</v>
+        <v>787</v>
       </c>
       <c r="S90" t="n">
-        <v>1761</v>
+        <v>787</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
@@ -9765,40 +9765,40 @@
         <v>2054</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0198</v>
+        <v>0.0086</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2937</v>
+        <v>0.2483</v>
       </c>
       <c r="J91" t="n">
-        <v>3.3143</v>
+        <v>6.8367</v>
       </c>
       <c r="K91" t="n">
-        <v>10.3545</v>
+        <v>23.198</v>
       </c>
       <c r="L91" t="n">
-        <v>0.058</v>
+        <v>0.0119</v>
       </c>
       <c r="M91" t="n">
-        <v>52.9178</v>
+        <v>170.9092</v>
       </c>
       <c r="N91" t="n">
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>175.625</v>
+        <v>83.75</v>
       </c>
       <c r="P91" t="n">
         <v>20</v>
       </c>
       <c r="Q91" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="R91" t="n">
-        <v>1757</v>
+        <v>799</v>
       </c>
       <c r="S91" t="n">
-        <v>1757</v>
+        <v>799</v>
       </c>
       <c r="T91" t="n">
         <v>0</v>
@@ -9833,40 +9833,40 @@
         <v>2025</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0258</v>
+        <v>0.0081</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4734</v>
+        <v>0.1924</v>
       </c>
       <c r="J92" t="n">
-        <v>2.5142</v>
+        <v>2.5417</v>
       </c>
       <c r="K92" t="n">
-        <v>5.2367</v>
+        <v>5.21</v>
       </c>
       <c r="L92" t="n">
-        <v>0.0771</v>
+        <v>0.0104</v>
       </c>
       <c r="M92" t="n">
-        <v>26.191</v>
+        <v>25.6094</v>
       </c>
       <c r="N92" t="n">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>182.25</v>
+        <v>77</v>
       </c>
       <c r="P92" t="n">
-        <v>15.1237</v>
+        <v>6.4896</v>
       </c>
       <c r="Q92" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R92" t="n">
-        <v>1806</v>
+        <v>770</v>
       </c>
       <c r="S92" t="n">
-        <v>1806</v>
+        <v>770</v>
       </c>
       <c r="T92" t="n">
         <v>0</v>
@@ -9901,40 +9901,40 @@
         <v>2026</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0245</v>
+        <v>0.0081</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4926</v>
+        <v>0.233</v>
       </c>
       <c r="J93" t="n">
-        <v>2.4035</v>
+        <v>2.5096</v>
       </c>
       <c r="K93" t="n">
-        <v>5.3668</v>
+        <v>5.0763</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0726</v>
+        <v>0.0108</v>
       </c>
       <c r="M93" t="n">
-        <v>25.386</v>
+        <v>24.2972</v>
       </c>
       <c r="N93" t="n">
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>177.625</v>
+        <v>80.25</v>
       </c>
       <c r="P93" t="n">
-        <v>14.5979</v>
+        <v>6.6667</v>
       </c>
       <c r="Q93" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R93" t="n">
-        <v>1769</v>
+        <v>786</v>
       </c>
       <c r="S93" t="n">
-        <v>1769</v>
+        <v>786</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
@@ -9969,40 +9969,40 @@
         <v>2027</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0231</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3943</v>
+        <v>0.2228</v>
       </c>
       <c r="J94" t="n">
-        <v>2.5567</v>
+        <v>2.4889</v>
       </c>
       <c r="K94" t="n">
-        <v>5.3132</v>
+        <v>4.999</v>
       </c>
       <c r="L94" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0114</v>
       </c>
       <c r="M94" t="n">
-        <v>24.0573</v>
+        <v>26.3893</v>
       </c>
       <c r="N94" t="n">
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>173.125</v>
+        <v>78.375</v>
       </c>
       <c r="P94" t="n">
-        <v>14.3958</v>
+        <v>6.5312</v>
       </c>
       <c r="Q94" t="n">
         <v>96</v>
       </c>
       <c r="R94" t="n">
-        <v>1742</v>
+        <v>789</v>
       </c>
       <c r="S94" t="n">
-        <v>1742</v>
+        <v>789</v>
       </c>
       <c r="T94" t="n">
         <v>0</v>
@@ -10037,40 +10037,40 @@
         <v>2028</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0242</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3424</v>
+        <v>0.2223</v>
       </c>
       <c r="J95" t="n">
-        <v>2.46</v>
+        <v>2.5522</v>
       </c>
       <c r="K95" t="n">
-        <v>5.1343</v>
+        <v>5.1106</v>
       </c>
       <c r="L95" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0106</v>
       </c>
       <c r="M95" t="n">
-        <v>23.9798</v>
+        <v>24.9611</v>
       </c>
       <c r="N95" t="n">
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>174.875</v>
+        <v>80.375</v>
       </c>
       <c r="P95" t="n">
-        <v>14.4948</v>
+        <v>6.7292</v>
       </c>
       <c r="Q95" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R95" t="n">
-        <v>1779</v>
+        <v>793</v>
       </c>
       <c r="S95" t="n">
-        <v>1779</v>
+        <v>793</v>
       </c>
       <c r="T95" t="n">
         <v>0</v>
@@ -10105,40 +10105,40 @@
         <v>2029</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0241</v>
+        <v>0.0074</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3363</v>
+        <v>0.1989</v>
       </c>
       <c r="J96" t="n">
-        <v>2.5133</v>
+        <v>2.4892</v>
       </c>
       <c r="K96" t="n">
-        <v>5.1932</v>
+        <v>5.0578</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0731</v>
+        <v>0.01</v>
       </c>
       <c r="M96" t="n">
-        <v>24.3319</v>
+        <v>23.9543</v>
       </c>
       <c r="N96" t="n">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>181.625</v>
+        <v>81.625</v>
       </c>
       <c r="P96" t="n">
-        <v>14.9897</v>
+        <v>6.8646</v>
       </c>
       <c r="Q96" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R96" t="n">
-        <v>1815</v>
+        <v>829</v>
       </c>
       <c r="S96" t="n">
-        <v>1815</v>
+        <v>829</v>
       </c>
       <c r="T96" t="n">
         <v>0</v>
@@ -10173,40 +10173,40 @@
         <v>2030</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0248</v>
+        <v>0.008</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3004</v>
+        <v>0.264</v>
       </c>
       <c r="J97" t="n">
-        <v>2.5336</v>
+        <v>2.5349</v>
       </c>
       <c r="K97" t="n">
-        <v>5.1713</v>
+        <v>5.1371</v>
       </c>
       <c r="L97" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="M97" t="n">
-        <v>25.4491</v>
+        <v>25.1633</v>
       </c>
       <c r="N97" t="n">
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>183</v>
+        <v>76.625</v>
       </c>
       <c r="P97" t="n">
-        <v>15.1753</v>
+        <v>6.4271</v>
       </c>
       <c r="Q97" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R97" t="n">
-        <v>1816</v>
+        <v>754</v>
       </c>
       <c r="S97" t="n">
-        <v>1816</v>
+        <v>754</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
@@ -10241,40 +10241,40 @@
         <v>2031</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0253</v>
+        <v>0.0071</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5646</v>
+        <v>0.1519</v>
       </c>
       <c r="J98" t="n">
-        <v>2.5005</v>
+        <v>2.5234</v>
       </c>
       <c r="K98" t="n">
-        <v>5.2299</v>
+        <v>5.0948</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0786</v>
+        <v>0.0094</v>
       </c>
       <c r="M98" t="n">
-        <v>25.4938</v>
+        <v>24.3571</v>
       </c>
       <c r="N98" t="n">
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>186.5</v>
+        <v>79.25</v>
       </c>
       <c r="P98" t="n">
-        <v>15.3711</v>
+        <v>6.5938</v>
       </c>
       <c r="Q98" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R98" t="n">
-        <v>1873</v>
+        <v>780</v>
       </c>
       <c r="S98" t="n">
-        <v>1873</v>
+        <v>780</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -10309,40 +10309,40 @@
         <v>2032</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0247</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2622</v>
+        <v>0.215</v>
       </c>
       <c r="J99" t="n">
-        <v>2.506</v>
+        <v>2.7225</v>
       </c>
       <c r="K99" t="n">
-        <v>5.1814</v>
+        <v>5.0388</v>
       </c>
       <c r="L99" t="n">
-        <v>0.0726</v>
+        <v>0.0103</v>
       </c>
       <c r="M99" t="n">
-        <v>25.4136</v>
+        <v>25.8559</v>
       </c>
       <c r="N99" t="n">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>176.5</v>
+        <v>75.5</v>
       </c>
       <c r="P99" t="n">
-        <v>14.6598</v>
+        <v>6.2604</v>
       </c>
       <c r="Q99" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R99" t="n">
-        <v>1772</v>
+        <v>772</v>
       </c>
       <c r="S99" t="n">
-        <v>1772</v>
+        <v>772</v>
       </c>
       <c r="T99" t="n">
         <v>0</v>
@@ -10377,40 +10377,40 @@
         <v>2033</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0305</v>
+        <v>0.0076</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4664</v>
+        <v>0.1559</v>
       </c>
       <c r="J100" t="n">
-        <v>2.4685</v>
+        <v>2.4382</v>
       </c>
       <c r="K100" t="n">
-        <v>5.1864</v>
+        <v>5.0441</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0906</v>
+        <v>0.0098</v>
       </c>
       <c r="M100" t="n">
-        <v>24.9012</v>
+        <v>24.2178</v>
       </c>
       <c r="N100" t="n">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>178.375</v>
+        <v>77.375</v>
       </c>
       <c r="P100" t="n">
-        <v>14.6701</v>
+        <v>6.5104</v>
       </c>
       <c r="Q100" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R100" t="n">
-        <v>1772</v>
+        <v>783</v>
       </c>
       <c r="S100" t="n">
-        <v>1772</v>
+        <v>783</v>
       </c>
       <c r="T100" t="n">
         <v>0</v>
@@ -10445,40 +10445,40 @@
         <v>2034</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0242</v>
+        <v>0.0089</v>
       </c>
       <c r="I101" t="n">
-        <v>0.3336</v>
+        <v>0.217</v>
       </c>
       <c r="J101" t="n">
-        <v>2.4479</v>
+        <v>2.486</v>
       </c>
       <c r="K101" t="n">
-        <v>5.1526</v>
+        <v>5.1074</v>
       </c>
       <c r="L101" t="n">
-        <v>0.0725</v>
+        <v>0.0119</v>
       </c>
       <c r="M101" t="n">
-        <v>24.5567</v>
+        <v>23.5371</v>
       </c>
       <c r="N101" t="n">
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>179.75</v>
+        <v>80.375</v>
       </c>
       <c r="P101" t="n">
-        <v>14.8041</v>
+        <v>6.7083</v>
       </c>
       <c r="Q101" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R101" t="n">
-        <v>1796</v>
+        <v>800</v>
       </c>
       <c r="S101" t="n">
-        <v>1796</v>
+        <v>800</v>
       </c>
       <c r="T101" t="n">
         <v>0</v>
@@ -10513,40 +10513,40 @@
         <v>2035</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0261</v>
+        <v>0.0073</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3796</v>
+        <v>0.1635</v>
       </c>
       <c r="J102" t="n">
-        <v>2.4157</v>
+        <v>2.5638</v>
       </c>
       <c r="K102" t="n">
-        <v>5.2187</v>
+        <v>5.1246</v>
       </c>
       <c r="L102" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="M102" t="n">
-        <v>23.5632</v>
+        <v>24.559</v>
       </c>
       <c r="N102" t="n">
         <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>188.5</v>
+        <v>84.125</v>
       </c>
       <c r="P102" t="n">
-        <v>15.3469</v>
+        <v>6.9688</v>
       </c>
       <c r="Q102" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R102" t="n">
-        <v>1842</v>
+        <v>821</v>
       </c>
       <c r="S102" t="n">
-        <v>1842</v>
+        <v>821</v>
       </c>
       <c r="T102" t="n">
         <v>0</v>
@@ -10581,40 +10581,40 @@
         <v>2036</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0255</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4292</v>
+        <v>0.2266</v>
       </c>
       <c r="J103" t="n">
-        <v>2.503</v>
+        <v>2.5459</v>
       </c>
       <c r="K103" t="n">
-        <v>5.1798</v>
+        <v>5.0691</v>
       </c>
       <c r="L103" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0121</v>
       </c>
       <c r="M103" t="n">
-        <v>24.6228</v>
+        <v>25.5042</v>
       </c>
       <c r="N103" t="n">
         <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>180.875</v>
+        <v>80.375</v>
       </c>
       <c r="P103" t="n">
-        <v>14.9175</v>
+        <v>6.6458</v>
       </c>
       <c r="Q103" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R103" t="n">
-        <v>1804</v>
+        <v>776</v>
       </c>
       <c r="S103" t="n">
-        <v>1804</v>
+        <v>776</v>
       </c>
       <c r="T103" t="n">
         <v>0</v>
@@ -10649,40 +10649,40 @@
         <v>2037</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0207</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3557</v>
+        <v>0.2328</v>
       </c>
       <c r="J104" t="n">
-        <v>2.4812</v>
+        <v>2.5517</v>
       </c>
       <c r="K104" t="n">
-        <v>5.2268</v>
+        <v>5.1232</v>
       </c>
       <c r="L104" t="n">
-        <v>0.0604</v>
+        <v>0.0126</v>
       </c>
       <c r="M104" t="n">
-        <v>24.1997</v>
+        <v>24.4369</v>
       </c>
       <c r="N104" t="n">
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>175.875</v>
+        <v>80.75</v>
       </c>
       <c r="P104" t="n">
-        <v>14.5155</v>
+        <v>6.7083</v>
       </c>
       <c r="Q104" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R104" t="n">
-        <v>1765</v>
+        <v>797</v>
       </c>
       <c r="S104" t="n">
-        <v>1765</v>
+        <v>797</v>
       </c>
       <c r="T104" t="n">
         <v>0</v>
@@ -10717,40 +10717,40 @@
         <v>2038</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0272</v>
+        <v>0.0115</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4164</v>
+        <v>0.3346</v>
       </c>
       <c r="J105" t="n">
-        <v>2.5448</v>
+        <v>2.5503</v>
       </c>
       <c r="K105" t="n">
-        <v>5.2918</v>
+        <v>5.1778</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0786</v>
+        <v>0.0163</v>
       </c>
       <c r="M105" t="n">
-        <v>23.9284</v>
+        <v>26.1206</v>
       </c>
       <c r="N105" t="n">
         <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>173.75</v>
+        <v>85.375</v>
       </c>
       <c r="P105" t="n">
-        <v>14.3542</v>
+        <v>7.0938</v>
       </c>
       <c r="Q105" t="n">
         <v>96</v>
       </c>
       <c r="R105" t="n">
-        <v>1752</v>
+        <v>833</v>
       </c>
       <c r="S105" t="n">
-        <v>1752</v>
+        <v>833</v>
       </c>
       <c r="T105" t="n">
         <v>0</v>
@@ -10785,40 +10785,40 @@
         <v>2039</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0217</v>
+        <v>0.008</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4042</v>
+        <v>0.2506</v>
       </c>
       <c r="J106" t="n">
-        <v>2.4982</v>
+        <v>2.5816</v>
       </c>
       <c r="K106" t="n">
-        <v>5.235</v>
+        <v>5.0947</v>
       </c>
       <c r="L106" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="M106" t="n">
-        <v>24.1169</v>
+        <v>25.0137</v>
       </c>
       <c r="N106" t="n">
         <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>181.5</v>
+        <v>77.75</v>
       </c>
       <c r="P106" t="n">
-        <v>14.9897</v>
+        <v>6.4896</v>
       </c>
       <c r="Q106" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R106" t="n">
-        <v>1801</v>
+        <v>781</v>
       </c>
       <c r="S106" t="n">
-        <v>1801</v>
+        <v>781</v>
       </c>
       <c r="T106" t="n">
         <v>0</v>
@@ -10853,40 +10853,40 @@
         <v>2040</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0249</v>
+        <v>0.0076</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3126</v>
+        <v>0.1684</v>
       </c>
       <c r="J107" t="n">
-        <v>2.5004</v>
+        <v>2.5294</v>
       </c>
       <c r="K107" t="n">
-        <v>5.2073</v>
+        <v>5.048</v>
       </c>
       <c r="L107" t="n">
-        <v>0.073</v>
+        <v>0.0105</v>
       </c>
       <c r="M107" t="n">
-        <v>24.5707</v>
+        <v>25.2242</v>
       </c>
       <c r="N107" t="n">
         <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>176.125</v>
+        <v>83.625</v>
       </c>
       <c r="P107" t="n">
-        <v>14.4536</v>
+        <v>6.9375</v>
       </c>
       <c r="Q107" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R107" t="n">
-        <v>1786</v>
+        <v>814</v>
       </c>
       <c r="S107" t="n">
-        <v>1786</v>
+        <v>814</v>
       </c>
       <c r="T107" t="n">
         <v>0</v>
@@ -10921,40 +10921,40 @@
         <v>2041</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0242</v>
+        <v>0.0066</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3373</v>
+        <v>0.224</v>
       </c>
       <c r="J108" t="n">
-        <v>2.4686</v>
+        <v>2.5073</v>
       </c>
       <c r="K108" t="n">
-        <v>5.1833</v>
+        <v>5.1102</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0718</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="M108" t="n">
-        <v>25.5339</v>
+        <v>26.199</v>
       </c>
       <c r="N108" t="n">
         <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>177.875</v>
+        <v>79.125</v>
       </c>
       <c r="P108" t="n">
-        <v>14.7423</v>
+        <v>6.5625</v>
       </c>
       <c r="Q108" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R108" t="n">
-        <v>1787</v>
+        <v>787</v>
       </c>
       <c r="S108" t="n">
-        <v>1787</v>
+        <v>787</v>
       </c>
       <c r="T108" t="n">
         <v>0</v>
@@ -10989,40 +10989,40 @@
         <v>2042</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0217</v>
+        <v>0.0091</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4349</v>
+        <v>0.223</v>
       </c>
       <c r="J109" t="n">
-        <v>2.5257</v>
+        <v>2.5984</v>
       </c>
       <c r="K109" t="n">
-        <v>5.315</v>
+        <v>5.21</v>
       </c>
       <c r="L109" t="n">
-        <v>0.0643</v>
+        <v>0.0124</v>
       </c>
       <c r="M109" t="n">
-        <v>22.6302</v>
+        <v>25.8821</v>
       </c>
       <c r="N109" t="n">
         <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>177.625</v>
+        <v>81.5</v>
       </c>
       <c r="P109" t="n">
-        <v>14.7708</v>
+        <v>6.7917</v>
       </c>
       <c r="Q109" t="n">
         <v>96</v>
       </c>
       <c r="R109" t="n">
-        <v>1795</v>
+        <v>821</v>
       </c>
       <c r="S109" t="n">
-        <v>1795</v>
+        <v>821</v>
       </c>
       <c r="T109" t="n">
         <v>0</v>
@@ -11057,40 +11057,40 @@
         <v>2043</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0263</v>
+        <v>0.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.432</v>
+        <v>0.2246</v>
       </c>
       <c r="J110" t="n">
-        <v>2.4706</v>
+        <v>2.4852</v>
       </c>
       <c r="K110" t="n">
-        <v>5.223</v>
+        <v>5.0602</v>
       </c>
       <c r="L110" t="n">
-        <v>0.0796</v>
+        <v>0.0127</v>
       </c>
       <c r="M110" t="n">
-        <v>25.1699</v>
+        <v>24.8003</v>
       </c>
       <c r="N110" t="n">
         <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>181.75</v>
+        <v>76.375</v>
       </c>
       <c r="P110" t="n">
-        <v>14.9184</v>
+        <v>6.3542</v>
       </c>
       <c r="Q110" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R110" t="n">
-        <v>1800</v>
+        <v>790</v>
       </c>
       <c r="S110" t="n">
-        <v>1800</v>
+        <v>790</v>
       </c>
       <c r="T110" t="n">
         <v>0</v>
@@ -11125,40 +11125,40 @@
         <v>2044</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0229</v>
+        <v>0.0073</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4194</v>
+        <v>0.1904</v>
       </c>
       <c r="J111" t="n">
-        <v>2.4752</v>
+        <v>2.5306</v>
       </c>
       <c r="K111" t="n">
-        <v>5.1726</v>
+        <v>5.1026</v>
       </c>
       <c r="L111" t="n">
-        <v>0.0684</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M111" t="n">
-        <v>25.7948</v>
+        <v>26.1798</v>
       </c>
       <c r="N111" t="n">
         <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>179.125</v>
+        <v>79</v>
       </c>
       <c r="P111" t="n">
-        <v>14.7526</v>
+        <v>6.5729</v>
       </c>
       <c r="Q111" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R111" t="n">
-        <v>1786</v>
+        <v>797</v>
       </c>
       <c r="S111" t="n">
-        <v>1786</v>
+        <v>797</v>
       </c>
       <c r="T111" t="n">
         <v>0</v>
@@ -11193,40 +11193,40 @@
         <v>2045</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0249</v>
+        <v>0.0081</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4505</v>
+        <v>0.231</v>
       </c>
       <c r="J112" t="n">
-        <v>2.4489</v>
+        <v>2.4626</v>
       </c>
       <c r="K112" t="n">
-        <v>5.1516</v>
+        <v>5.105</v>
       </c>
       <c r="L112" t="n">
-        <v>0.0747</v>
+        <v>0.0109</v>
       </c>
       <c r="M112" t="n">
-        <v>24.2032</v>
+        <v>25.6323</v>
       </c>
       <c r="N112" t="n">
         <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>180.125</v>
+        <v>81</v>
       </c>
       <c r="P112" t="n">
-        <v>14.9688</v>
+        <v>6.75</v>
       </c>
       <c r="Q112" t="n">
         <v>96</v>
       </c>
       <c r="R112" t="n">
-        <v>1795</v>
+        <v>803</v>
       </c>
       <c r="S112" t="n">
-        <v>1795</v>
+        <v>803</v>
       </c>
       <c r="T112" t="n">
         <v>0</v>
@@ -11261,40 +11261,40 @@
         <v>2046</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0251</v>
+        <v>0.0127</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3534</v>
+        <v>0.3325</v>
       </c>
       <c r="J113" t="n">
-        <v>2.5019</v>
+        <v>2.5143</v>
       </c>
       <c r="K113" t="n">
-        <v>5.3314</v>
+        <v>5.2657</v>
       </c>
       <c r="L113" t="n">
-        <v>0.0771</v>
+        <v>0.0173</v>
       </c>
       <c r="M113" t="n">
-        <v>24.1569</v>
+        <v>26.1876</v>
       </c>
       <c r="N113" t="n">
         <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>184.5</v>
+        <v>81.25</v>
       </c>
       <c r="P113" t="n">
-        <v>15.3542</v>
+        <v>6.7917</v>
       </c>
       <c r="Q113" t="n">
         <v>96</v>
       </c>
       <c r="R113" t="n">
-        <v>1854</v>
+        <v>805</v>
       </c>
       <c r="S113" t="n">
-        <v>1854</v>
+        <v>805</v>
       </c>
       <c r="T113" t="n">
         <v>0</v>
@@ -11329,40 +11329,40 @@
         <v>2047</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0302</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4302</v>
+        <v>0.2135</v>
       </c>
       <c r="J114" t="n">
-        <v>2.5674</v>
+        <v>2.6041</v>
       </c>
       <c r="K114" t="n">
-        <v>5.2897</v>
+        <v>5.0766</v>
       </c>
       <c r="L114" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0135</v>
       </c>
       <c r="M114" t="n">
-        <v>24.22</v>
+        <v>25.6756</v>
       </c>
       <c r="N114" t="n">
         <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>183.625</v>
+        <v>83.875</v>
       </c>
       <c r="P114" t="n">
-        <v>15.0412</v>
+        <v>6.9479</v>
       </c>
       <c r="Q114" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R114" t="n">
-        <v>1855</v>
+        <v>845</v>
       </c>
       <c r="S114" t="n">
-        <v>1855</v>
+        <v>845</v>
       </c>
       <c r="T114" t="n">
         <v>0</v>
@@ -11397,40 +11397,40 @@
         <v>2048</v>
       </c>
       <c r="H115" t="n">
-        <v>0.025</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3201</v>
+        <v>0.2524</v>
       </c>
       <c r="J115" t="n">
-        <v>2.5137</v>
+        <v>2.4745</v>
       </c>
       <c r="K115" t="n">
-        <v>5.1152</v>
+        <v>5.0221</v>
       </c>
       <c r="L115" t="n">
-        <v>0.0761</v>
+        <v>0.0125</v>
       </c>
       <c r="M115" t="n">
-        <v>24.2851</v>
+        <v>25.8332</v>
       </c>
       <c r="N115" t="n">
         <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>182.875</v>
+        <v>83.375</v>
       </c>
       <c r="P115" t="n">
-        <v>15.0825</v>
+        <v>6.9271</v>
       </c>
       <c r="Q115" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R115" t="n">
-        <v>1819</v>
+        <v>822</v>
       </c>
       <c r="S115" t="n">
-        <v>1819</v>
+        <v>822</v>
       </c>
       <c r="T115" t="n">
         <v>0</v>
@@ -11465,40 +11465,40 @@
         <v>2049</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0219</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3579</v>
+        <v>0.2591</v>
       </c>
       <c r="J116" t="n">
-        <v>2.5376</v>
+        <v>2.4902</v>
       </c>
       <c r="K116" t="n">
-        <v>5.2603</v>
+        <v>5.1272</v>
       </c>
       <c r="L116" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0111</v>
       </c>
       <c r="M116" t="n">
-        <v>24.1342</v>
+        <v>24.7953</v>
       </c>
       <c r="N116" t="n">
         <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>178.5</v>
+        <v>80.75</v>
       </c>
       <c r="P116" t="n">
-        <v>14.7423</v>
+        <v>6.7708</v>
       </c>
       <c r="Q116" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R116" t="n">
-        <v>1754</v>
+        <v>807</v>
       </c>
       <c r="S116" t="n">
-        <v>1754</v>
+        <v>807</v>
       </c>
       <c r="T116" t="n">
         <v>0</v>
@@ -11533,40 +11533,40 @@
         <v>2050</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0237</v>
+        <v>0.0104</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4288</v>
+        <v>0.2246</v>
       </c>
       <c r="J117" t="n">
-        <v>2.4818</v>
+        <v>2.6006</v>
       </c>
       <c r="K117" t="n">
-        <v>5.1568</v>
+        <v>5.1167</v>
       </c>
       <c r="L117" t="n">
-        <v>0.0731</v>
+        <v>0.0146</v>
       </c>
       <c r="M117" t="n">
-        <v>24.5513</v>
+        <v>23.4473</v>
       </c>
       <c r="N117" t="n">
         <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>185.25</v>
+        <v>83.875</v>
       </c>
       <c r="P117" t="n">
-        <v>15.1856</v>
+        <v>6.9479</v>
       </c>
       <c r="Q117" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R117" t="n">
-        <v>1831</v>
+        <v>837</v>
       </c>
       <c r="S117" t="n">
-        <v>1831</v>
+        <v>837</v>
       </c>
       <c r="T117" t="n">
         <v>0</v>
@@ -11601,40 +11601,40 @@
         <v>2051</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0238</v>
+        <v>0.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.303</v>
+        <v>0.2262</v>
       </c>
       <c r="J118" t="n">
-        <v>2.4947</v>
+        <v>2.5275</v>
       </c>
       <c r="K118" t="n">
-        <v>5.1876</v>
+        <v>5.0914</v>
       </c>
       <c r="L118" t="n">
-        <v>0.0709</v>
+        <v>0.0131</v>
       </c>
       <c r="M118" t="n">
-        <v>25.6245</v>
+        <v>24.5783</v>
       </c>
       <c r="N118" t="n">
         <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>178.75</v>
+        <v>79</v>
       </c>
       <c r="P118" t="n">
-        <v>14.7292</v>
+        <v>6.625</v>
       </c>
       <c r="Q118" t="n">
         <v>96</v>
       </c>
       <c r="R118" t="n">
-        <v>1767</v>
+        <v>787</v>
       </c>
       <c r="S118" t="n">
-        <v>1767</v>
+        <v>787</v>
       </c>
       <c r="T118" t="n">
         <v>0</v>
@@ -11669,40 +11669,40 @@
         <v>2052</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0249</v>
+        <v>0.0076</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4329</v>
+        <v>0.2606</v>
       </c>
       <c r="J119" t="n">
-        <v>2.478</v>
+        <v>2.527</v>
       </c>
       <c r="K119" t="n">
-        <v>5.2264</v>
+        <v>5.0395</v>
       </c>
       <c r="L119" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="M119" t="n">
-        <v>23.7531</v>
+        <v>24.0282</v>
       </c>
       <c r="N119" t="n">
         <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>186</v>
+        <v>73.75</v>
       </c>
       <c r="P119" t="n">
-        <v>15.4124</v>
+        <v>6.1875</v>
       </c>
       <c r="Q119" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R119" t="n">
-        <v>1823</v>
+        <v>758</v>
       </c>
       <c r="S119" t="n">
-        <v>1823</v>
+        <v>758</v>
       </c>
       <c r="T119" t="n">
         <v>0</v>
@@ -11737,40 +11737,40 @@
         <v>2053</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0231</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3259</v>
+        <v>0.1872</v>
       </c>
       <c r="J120" t="n">
-        <v>2.544</v>
+        <v>2.5643</v>
       </c>
       <c r="K120" t="n">
-        <v>5.1805</v>
+        <v>5.155</v>
       </c>
       <c r="L120" t="n">
-        <v>0.0684</v>
+        <v>0.0113</v>
       </c>
       <c r="M120" t="n">
-        <v>25.586</v>
+        <v>26.2066</v>
       </c>
       <c r="N120" t="n">
         <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>177.875</v>
+        <v>82.625</v>
       </c>
       <c r="P120" t="n">
-        <v>14.75</v>
+        <v>6.9062</v>
       </c>
       <c r="Q120" t="n">
         <v>96</v>
       </c>
       <c r="R120" t="n">
-        <v>1804</v>
+        <v>820</v>
       </c>
       <c r="S120" t="n">
-        <v>1804</v>
+        <v>820</v>
       </c>
       <c r="T120" t="n">
         <v>0</v>
@@ -11805,40 +11805,40 @@
         <v>2054</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0226</v>
+        <v>0.0108</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3503</v>
+        <v>0.281</v>
       </c>
       <c r="J121" t="n">
-        <v>2.492</v>
+        <v>2.5238</v>
       </c>
       <c r="K121" t="n">
-        <v>5.1379</v>
+        <v>5.281</v>
       </c>
       <c r="L121" t="n">
-        <v>0.0649</v>
+        <v>0.0145</v>
       </c>
       <c r="M121" t="n">
-        <v>25.0613</v>
+        <v>24.4444</v>
       </c>
       <c r="N121" t="n">
         <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>172</v>
+        <v>80.875</v>
       </c>
       <c r="P121" t="n">
-        <v>14.1979</v>
+        <v>6.7396</v>
       </c>
       <c r="Q121" t="n">
         <v>96</v>
       </c>
       <c r="R121" t="n">
-        <v>1733</v>
+        <v>787</v>
       </c>
       <c r="S121" t="n">
-        <v>1733</v>
+        <v>787</v>
       </c>
       <c r="T121" t="n">
         <v>0</v>
